--- a/research/traditional_assets/database/data/new_zealand/new_zealand_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_retail_building_supply.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08706475818401804</v>
+        <v>0.08685337686110281</v>
       </c>
       <c r="C2">
-        <v>730.5629776477481</v>
+        <v>725.5792173339868</v>
       </c>
       <c r="D2">
-        <v>652.9629776477481</v>
+        <v>655.9392173339868</v>
       </c>
       <c r="E2">
-        <v>-168.4</v>
+        <v>-160.44</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.96</v>
       </c>
       <c r="G2">
         <v>77.59999999999999</v>
@@ -1457,28 +1457,28 @@
         <v>71.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.400388</v>
       </c>
       <c r="N2">
-        <v>71.3</v>
+        <v>70.89961199999999</v>
       </c>
       <c r="O2">
-        <v>19.964</v>
+        <v>19.85189136</v>
       </c>
       <c r="P2">
-        <v>51.336</v>
+        <v>51.04772063999999</v>
       </c>
       <c r="Q2">
-        <v>57.836</v>
+        <v>57.54772063999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08706475818401804</v>
+        <v>0.08736486551626546</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.9599276100754147</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>178.0772650528987</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08685337686110281</v>
+        <v>0.08664199553818755</v>
       </c>
       <c r="C3">
-        <v>725.5792173339868</v>
+        <v>720.6227129691634</v>
       </c>
       <c r="D3">
-        <v>655.9392173339868</v>
+        <v>658.9427129691634</v>
       </c>
       <c r="E3">
-        <v>-160.44</v>
+        <v>-152.48</v>
       </c>
       <c r="F3">
-        <v>7.96</v>
+        <v>15.92</v>
       </c>
       <c r="G3">
         <v>77.59999999999999</v>
@@ -1539,28 +1539,28 @@
         <v>71.3</v>
       </c>
       <c r="M3">
-        <v>0.400388</v>
+        <v>0.8007759999999999</v>
       </c>
       <c r="N3">
-        <v>70.89961199999999</v>
+        <v>70.499224</v>
       </c>
       <c r="O3">
-        <v>19.85189136</v>
+        <v>19.73978272</v>
       </c>
       <c r="P3">
-        <v>51.04772063999999</v>
+        <v>50.75944128</v>
       </c>
       <c r="Q3">
-        <v>57.54772063999999</v>
+        <v>57.25944128</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08736486551626546</v>
+        <v>0.08767109748794648</v>
       </c>
       <c r="T3">
-        <v>0.9599276100754147</v>
+        <v>0.9669999419849071</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>178.0772650528987</v>
+        <v>89.03863252644935</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08664199553818755</v>
+        <v>0.0864306142152723</v>
       </c>
       <c r="C4">
-        <v>720.6227129691634</v>
+        <v>715.6938406842849</v>
       </c>
       <c r="D4">
-        <v>658.9427129691634</v>
+        <v>661.9738406842848</v>
       </c>
       <c r="E4">
-        <v>-152.48</v>
+        <v>-144.52</v>
       </c>
       <c r="F4">
-        <v>15.92</v>
+        <v>23.88</v>
       </c>
       <c r="G4">
         <v>77.59999999999999</v>
@@ -1621,28 +1621,28 @@
         <v>71.3</v>
       </c>
       <c r="M4">
-        <v>0.8007759999999999</v>
+        <v>1.201164</v>
       </c>
       <c r="N4">
-        <v>70.499224</v>
+        <v>70.09883599999999</v>
       </c>
       <c r="O4">
-        <v>19.73978272</v>
+        <v>19.62767408</v>
       </c>
       <c r="P4">
-        <v>50.75944128</v>
+        <v>50.47116191999999</v>
       </c>
       <c r="Q4">
-        <v>57.25944128</v>
+        <v>56.97116191999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08767109748794648</v>
+        <v>0.08798364352089928</v>
       </c>
       <c r="T4">
-        <v>0.9669999419849071</v>
+        <v>0.9742180951708841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>89.03863252644935</v>
+        <v>59.35908835096622</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0864306142152723</v>
+        <v>0.08621923289235706</v>
       </c>
       <c r="C5">
-        <v>715.6938406842849</v>
+        <v>710.7929835631326</v>
       </c>
       <c r="D5">
-        <v>661.9738406842848</v>
+        <v>665.0329835631326</v>
       </c>
       <c r="E5">
-        <v>-144.52</v>
+        <v>-136.56</v>
       </c>
       <c r="F5">
-        <v>23.88</v>
+        <v>31.84</v>
       </c>
       <c r="G5">
         <v>77.59999999999999</v>
@@ -1703,28 +1703,28 @@
         <v>71.3</v>
       </c>
       <c r="M5">
-        <v>1.201164</v>
+        <v>1.601552</v>
       </c>
       <c r="N5">
-        <v>70.09883599999999</v>
+        <v>69.698448</v>
       </c>
       <c r="O5">
-        <v>19.62767408</v>
+        <v>19.51556544</v>
       </c>
       <c r="P5">
-        <v>50.47116191999999</v>
+        <v>50.18288256</v>
       </c>
       <c r="Q5">
-        <v>56.97116191999999</v>
+        <v>56.68288256</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08798364352089928</v>
+        <v>0.0883027009295386</v>
       </c>
       <c r="T5">
-        <v>0.9742180951708841</v>
+        <v>0.9815866265482354</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.35908835096622</v>
+        <v>44.51931626322467</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08621923289235706</v>
+        <v>0.08600785156944178</v>
       </c>
       <c r="C6">
-        <v>710.7929835631326</v>
+        <v>705.9205318036591</v>
       </c>
       <c r="D6">
-        <v>665.0329835631326</v>
+        <v>668.120531803659</v>
       </c>
       <c r="E6">
-        <v>-136.56</v>
+        <v>-128.6</v>
       </c>
       <c r="F6">
-        <v>31.84</v>
+        <v>39.8</v>
       </c>
       <c r="G6">
         <v>77.59999999999999</v>
@@ -1785,28 +1785,28 @@
         <v>71.3</v>
       </c>
       <c r="M6">
-        <v>1.601552</v>
+        <v>2.00194</v>
       </c>
       <c r="N6">
-        <v>69.698448</v>
+        <v>69.29805999999999</v>
       </c>
       <c r="O6">
-        <v>19.51556544</v>
+        <v>19.4034568</v>
       </c>
       <c r="P6">
-        <v>50.18288256</v>
+        <v>49.89460319999999</v>
       </c>
       <c r="Q6">
-        <v>56.68288256</v>
+        <v>56.39460319999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0883027009295386</v>
+        <v>0.08862847533625451</v>
       </c>
       <c r="T6">
-        <v>0.9815866265482354</v>
+        <v>0.989110284901952</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.51931626322467</v>
+        <v>35.61545301057973</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08600785156944178</v>
+        <v>0.08579647024652655</v>
       </c>
       <c r="C7">
-        <v>705.9205318036591</v>
+        <v>701.0768828839022</v>
       </c>
       <c r="D7">
-        <v>668.120531803659</v>
+        <v>671.2368828839021</v>
       </c>
       <c r="E7">
-        <v>-128.6</v>
+        <v>-120.64</v>
       </c>
       <c r="F7">
-        <v>39.8</v>
+        <v>47.76000000000001</v>
       </c>
       <c r="G7">
         <v>77.59999999999999</v>
@@ -1867,28 +1867,28 @@
         <v>71.3</v>
       </c>
       <c r="M7">
-        <v>2.00194</v>
+        <v>2.402328</v>
       </c>
       <c r="N7">
-        <v>69.29805999999999</v>
+        <v>68.897672</v>
       </c>
       <c r="O7">
-        <v>19.4034568</v>
+        <v>19.29134816</v>
       </c>
       <c r="P7">
-        <v>49.89460319999999</v>
+        <v>49.60632384</v>
       </c>
       <c r="Q7">
-        <v>56.39460319999999</v>
+        <v>56.10632384</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08862847533625451</v>
+        <v>0.08896118111332611</v>
       </c>
       <c r="T7">
-        <v>0.989110284901952</v>
+        <v>0.9967940210929819</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.61545301057973</v>
+        <v>29.67954417548311</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08579647024652655</v>
+        <v>0.0855850889236113</v>
       </c>
       <c r="C8">
-        <v>701.0768828839022</v>
+        <v>696.262441732568</v>
       </c>
       <c r="D8">
-        <v>671.2368828839021</v>
+        <v>674.3824417325681</v>
       </c>
       <c r="E8">
-        <v>-120.64</v>
+        <v>-112.68</v>
       </c>
       <c r="F8">
-        <v>47.76</v>
+        <v>55.71999999999999</v>
       </c>
       <c r="G8">
         <v>77.59999999999999</v>
@@ -1949,28 +1949,28 @@
         <v>71.3</v>
       </c>
       <c r="M8">
-        <v>2.402328</v>
+        <v>2.802715999999999</v>
       </c>
       <c r="N8">
-        <v>68.897672</v>
+        <v>68.49728399999999</v>
       </c>
       <c r="O8">
-        <v>19.29134816</v>
+        <v>19.17923952</v>
       </c>
       <c r="P8">
-        <v>49.60632384</v>
+        <v>49.31804448</v>
       </c>
       <c r="Q8">
-        <v>56.10632384</v>
+        <v>55.81804448</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08896118111332611</v>
+        <v>0.08930104185334548</v>
       </c>
       <c r="T8">
-        <v>0.9967940210929819</v>
+        <v>1.004642998922529</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.67954417548312</v>
+        <v>25.43960929327125</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08558508892361129</v>
+        <v>0.08537370760069604</v>
       </c>
       <c r="C9">
-        <v>696.2624417325684</v>
+        <v>691.4776209044281</v>
       </c>
       <c r="D9">
-        <v>674.3824417325684</v>
+        <v>677.5576209044281</v>
       </c>
       <c r="E9">
-        <v>-112.68</v>
+        <v>-104.72</v>
       </c>
       <c r="F9">
-        <v>55.72000000000001</v>
+        <v>63.68</v>
       </c>
       <c r="G9">
         <v>77.59999999999999</v>
@@ -2031,28 +2031,28 @@
         <v>71.3</v>
       </c>
       <c r="M9">
-        <v>2.802716</v>
+        <v>3.203104</v>
       </c>
       <c r="N9">
-        <v>68.49728399999999</v>
+        <v>68.096896</v>
       </c>
       <c r="O9">
-        <v>19.17923952</v>
+        <v>19.06713088</v>
       </c>
       <c r="P9">
-        <v>49.31804448</v>
+        <v>49.02976512</v>
       </c>
       <c r="Q9">
-        <v>55.81804448</v>
+        <v>55.52976512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08930104185334548</v>
+        <v>0.08964829087032178</v>
       </c>
       <c r="T9">
-        <v>1.004642998922529</v>
+        <v>1.012662606704891</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.43960929327124</v>
+        <v>22.25965813161234</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08537370760069604</v>
+        <v>0.08516232627778079</v>
       </c>
       <c r="C10">
-        <v>691.4776209044281</v>
+        <v>686.7228407606956</v>
       </c>
       <c r="D10">
-        <v>677.5576209044281</v>
+        <v>680.7628407606956</v>
       </c>
       <c r="E10">
-        <v>-104.72</v>
+        <v>-96.76000000000001</v>
       </c>
       <c r="F10">
-        <v>63.68</v>
+        <v>71.64</v>
       </c>
       <c r="G10">
         <v>77.59999999999999</v>
@@ -2113,28 +2113,28 @@
         <v>71.3</v>
       </c>
       <c r="M10">
-        <v>3.203104</v>
+        <v>3.603492</v>
       </c>
       <c r="N10">
-        <v>68.096896</v>
+        <v>67.69650799999999</v>
       </c>
       <c r="O10">
-        <v>19.06713088</v>
+        <v>18.95502224</v>
       </c>
       <c r="P10">
-        <v>49.02976512</v>
+        <v>48.74148575999999</v>
       </c>
       <c r="Q10">
-        <v>55.52976512</v>
+        <v>55.24148575999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08964829087032178</v>
+        <v>0.09000317173382505</v>
       </c>
       <c r="T10">
-        <v>1.012662606704891</v>
+        <v>1.02085846960335</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.25965813161234</v>
+        <v>19.78636278365541</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08516232627778079</v>
+        <v>0.08495094495486556</v>
       </c>
       <c r="C11">
-        <v>686.7228407606956</v>
+        <v>681.9985296545493</v>
       </c>
       <c r="D11">
-        <v>680.7628407606956</v>
+        <v>683.9985296545493</v>
       </c>
       <c r="E11">
-        <v>-96.76000000000001</v>
+        <v>-88.80000000000001</v>
       </c>
       <c r="F11">
-        <v>71.64</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G11">
         <v>77.59999999999999</v>
@@ -2195,28 +2195,28 @@
         <v>71.3</v>
       </c>
       <c r="M11">
-        <v>3.603492</v>
+        <v>4.00388</v>
       </c>
       <c r="N11">
-        <v>67.69650799999999</v>
+        <v>67.29612</v>
       </c>
       <c r="O11">
-        <v>18.95502224</v>
+        <v>18.8429136</v>
       </c>
       <c r="P11">
-        <v>48.74148575999999</v>
+        <v>48.4532064</v>
       </c>
       <c r="Q11">
-        <v>55.24148575999999</v>
+        <v>54.9532064</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09000317173382505</v>
+        <v>0.0903659388387395</v>
       </c>
       <c r="T11">
-        <v>1.02085846960335</v>
+        <v>1.029236462788441</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.78636278365541</v>
+        <v>17.80772650528987</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08495094495486556</v>
+        <v>0.08473956363195029</v>
       </c>
       <c r="C12">
-        <v>681.9985296545493</v>
+        <v>677.3051241219705</v>
       </c>
       <c r="D12">
-        <v>683.9985296545493</v>
+        <v>687.2651241219705</v>
       </c>
       <c r="E12">
-        <v>-88.8</v>
+        <v>-80.84</v>
       </c>
       <c r="F12">
-        <v>79.60000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="G12">
         <v>77.59999999999999</v>
@@ -2277,28 +2277,28 @@
         <v>71.3</v>
       </c>
       <c r="M12">
-        <v>4.003880000000001</v>
+        <v>4.404268</v>
       </c>
       <c r="N12">
-        <v>67.29612</v>
+        <v>66.895732</v>
       </c>
       <c r="O12">
-        <v>18.8429136</v>
+        <v>18.73080496</v>
       </c>
       <c r="P12">
-        <v>48.4532064</v>
+        <v>48.16492703999999</v>
       </c>
       <c r="Q12">
-        <v>54.9532064</v>
+        <v>54.66492703999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0903659388387395</v>
+        <v>0.09073685801342729</v>
       </c>
       <c r="T12">
-        <v>1.029236462788441</v>
+        <v>1.037802725483309</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.80772650528987</v>
+        <v>16.18884227753625</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08473956363195029</v>
+        <v>0.08452818230903504</v>
       </c>
       <c r="C13">
-        <v>677.3051241219705</v>
+        <v>672.6430690780729</v>
       </c>
       <c r="D13">
-        <v>687.2651241219705</v>
+        <v>690.5630690780729</v>
       </c>
       <c r="E13">
-        <v>-80.84</v>
+        <v>-72.88000000000001</v>
       </c>
       <c r="F13">
-        <v>87.56</v>
+        <v>95.52</v>
       </c>
       <c r="G13">
         <v>77.59999999999999</v>
@@ -2359,28 +2359,28 @@
         <v>71.3</v>
       </c>
       <c r="M13">
-        <v>4.404268</v>
+        <v>4.804656</v>
       </c>
       <c r="N13">
-        <v>66.895732</v>
+        <v>66.495344</v>
       </c>
       <c r="O13">
-        <v>18.73080496</v>
+        <v>18.61869632</v>
       </c>
       <c r="P13">
-        <v>48.16492703999999</v>
+        <v>47.87664768</v>
       </c>
       <c r="Q13">
-        <v>54.66492703999999</v>
+        <v>54.37664768</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09073685801342729</v>
+        <v>0.091116207169358</v>
       </c>
       <c r="T13">
-        <v>1.037802725483309</v>
+        <v>1.046563675966698</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.18884227753625</v>
+        <v>14.83977208774156</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08452818230903504</v>
+        <v>0.08431680098611978</v>
       </c>
       <c r="C14">
-        <v>672.6430690780729</v>
+        <v>668.0128180191173</v>
       </c>
       <c r="D14">
-        <v>690.5630690780729</v>
+        <v>693.8928180191173</v>
       </c>
       <c r="E14">
-        <v>-72.88000000000001</v>
+        <v>-64.92</v>
       </c>
       <c r="F14">
-        <v>95.52</v>
+        <v>103.48</v>
       </c>
       <c r="G14">
         <v>77.59999999999999</v>
@@ -2441,28 +2441,28 @@
         <v>71.3</v>
       </c>
       <c r="M14">
-        <v>4.804656</v>
+        <v>5.205044</v>
       </c>
       <c r="N14">
-        <v>66.495344</v>
+        <v>66.094956</v>
       </c>
       <c r="O14">
-        <v>18.61869632</v>
+        <v>18.50658768</v>
       </c>
       <c r="P14">
-        <v>47.87664768</v>
+        <v>47.58836832</v>
       </c>
       <c r="Q14">
-        <v>54.37664768</v>
+        <v>54.08836832</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.091116207169358</v>
+        <v>0.09150427699553998</v>
       </c>
       <c r="T14">
-        <v>1.046563675966698</v>
+        <v>1.055526027610623</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.83977208774156</v>
+        <v>13.69825115791528</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08431680098611978</v>
+        <v>0.08425661966320454</v>
       </c>
       <c r="C15">
-        <v>668.0128180191173</v>
+        <v>661.0066947515475</v>
       </c>
       <c r="D15">
-        <v>693.8928180191173</v>
+        <v>694.8466947515475</v>
       </c>
       <c r="E15">
-        <v>-64.92</v>
+        <v>-56.95999999999999</v>
       </c>
       <c r="F15">
-        <v>103.48</v>
+        <v>111.44</v>
       </c>
       <c r="G15">
         <v>77.59999999999999</v>
@@ -2523,45 +2523,45 @@
         <v>71.3</v>
       </c>
       <c r="M15">
-        <v>5.205044</v>
+        <v>5.772592</v>
       </c>
       <c r="N15">
-        <v>66.094956</v>
+        <v>65.52740799999999</v>
       </c>
       <c r="O15">
-        <v>18.50658768</v>
+        <v>18.34767424</v>
       </c>
       <c r="P15">
-        <v>47.58836832</v>
+        <v>47.17973375999999</v>
       </c>
       <c r="Q15">
-        <v>54.08836832</v>
+        <v>53.67973375999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09150427699553998</v>
+        <v>0.09190137170140064</v>
       </c>
       <c r="T15">
-        <v>1.055526027610623</v>
+        <v>1.064696806036966</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.28</v>
       </c>
       <c r="W15">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.69825115791528</v>
+        <v>12.35147053524656</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08425661966320454</v>
+        <v>0.08405603834028928</v>
       </c>
       <c r="C16">
-        <v>661.0066947515475</v>
+        <v>656.2449418048288</v>
       </c>
       <c r="D16">
-        <v>694.8466947515475</v>
+        <v>698.0449418048288</v>
       </c>
       <c r="E16">
-        <v>-56.95999999999999</v>
+        <v>-48.99999999999999</v>
       </c>
       <c r="F16">
-        <v>111.44</v>
+        <v>119.4</v>
       </c>
       <c r="G16">
         <v>77.59999999999999</v>
@@ -2605,28 +2605,28 @@
         <v>71.3</v>
       </c>
       <c r="M16">
-        <v>5.772592</v>
+        <v>6.184920000000001</v>
       </c>
       <c r="N16">
-        <v>65.52740799999999</v>
+        <v>65.11507999999999</v>
       </c>
       <c r="O16">
-        <v>18.34767424</v>
+        <v>18.2322224</v>
       </c>
       <c r="P16">
-        <v>47.17973375999999</v>
+        <v>46.88285759999999</v>
       </c>
       <c r="Q16">
-        <v>53.67973375999999</v>
+        <v>53.38285759999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09190137170140064</v>
+        <v>0.09230780981210504</v>
       </c>
       <c r="T16">
-        <v>1.064696806036966</v>
+        <v>1.074083367485105</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.35147053524656</v>
+        <v>11.52803916623012</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08405603834028928</v>
+        <v>0.08385545701737404</v>
       </c>
       <c r="C17">
-        <v>656.2449418048288</v>
+        <v>651.5127668445795</v>
       </c>
       <c r="D17">
-        <v>698.0449418048288</v>
+        <v>701.2727668445795</v>
       </c>
       <c r="E17">
-        <v>-49.00000000000001</v>
+        <v>-41.04000000000001</v>
       </c>
       <c r="F17">
-        <v>119.4</v>
+        <v>127.36</v>
       </c>
       <c r="G17">
         <v>77.59999999999999</v>
@@ -2687,28 +2687,28 @@
         <v>71.3</v>
       </c>
       <c r="M17">
-        <v>6.184919999999999</v>
+        <v>6.597248</v>
       </c>
       <c r="N17">
-        <v>65.11507999999999</v>
+        <v>64.702752</v>
       </c>
       <c r="O17">
-        <v>18.2322224</v>
+        <v>18.11677056</v>
       </c>
       <c r="P17">
-        <v>46.88285759999999</v>
+        <v>46.58598144</v>
       </c>
       <c r="Q17">
-        <v>53.38285759999999</v>
+        <v>53.08598144</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09230780981210504</v>
+        <v>0.09272392502068338</v>
       </c>
       <c r="T17">
-        <v>1.074083367485105</v>
+        <v>1.083693418491533</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.52803916623012</v>
+        <v>10.80753671834074</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08385545701737404</v>
+        <v>0.08365487569445879</v>
       </c>
       <c r="C18">
-        <v>651.5127668445795</v>
+        <v>646.8105820910647</v>
       </c>
       <c r="D18">
-        <v>701.2727668445795</v>
+        <v>704.5305820910647</v>
       </c>
       <c r="E18">
-        <v>-41.04000000000001</v>
+        <v>-33.07999999999998</v>
       </c>
       <c r="F18">
-        <v>127.36</v>
+        <v>135.32</v>
       </c>
       <c r="G18">
         <v>77.59999999999999</v>
@@ -2769,28 +2769,28 @@
         <v>71.3</v>
       </c>
       <c r="M18">
-        <v>6.597248</v>
+        <v>7.009576000000001</v>
       </c>
       <c r="N18">
-        <v>64.702752</v>
+        <v>64.290424</v>
       </c>
       <c r="O18">
-        <v>18.11677056</v>
+        <v>18.00131872</v>
       </c>
       <c r="P18">
-        <v>46.58598144</v>
+        <v>46.28910528</v>
       </c>
       <c r="Q18">
-        <v>53.08598144</v>
+        <v>52.78910528</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09272392502068338</v>
+        <v>0.09315006710175758</v>
       </c>
       <c r="T18">
-        <v>1.083693418491533</v>
+        <v>1.093535036992092</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.80753671834074</v>
+        <v>10.17179926432069</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08365487569445879</v>
+        <v>0.08367461437154353</v>
       </c>
       <c r="C19">
-        <v>646.8105820910647</v>
+        <v>638.5286469522646</v>
       </c>
       <c r="D19">
-        <v>704.5305820910647</v>
+        <v>704.2086469522646</v>
       </c>
       <c r="E19">
-        <v>-33.07999999999998</v>
+        <v>-25.11999999999998</v>
       </c>
       <c r="F19">
-        <v>135.32</v>
+        <v>143.28</v>
       </c>
       <c r="G19">
         <v>77.59999999999999</v>
@@ -2851,45 +2851,45 @@
         <v>71.3</v>
       </c>
       <c r="M19">
-        <v>7.009576000000001</v>
+        <v>7.665480000000001</v>
       </c>
       <c r="N19">
-        <v>64.290424</v>
+        <v>63.63451999999999</v>
       </c>
       <c r="O19">
-        <v>18.00131872</v>
+        <v>17.8176656</v>
       </c>
       <c r="P19">
-        <v>46.28910528</v>
+        <v>45.8168544</v>
       </c>
       <c r="Q19">
-        <v>52.78910528</v>
+        <v>52.3168544</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09315006710175758</v>
+        <v>0.09358660289212625</v>
       </c>
       <c r="T19">
-        <v>1.093535036992092</v>
+        <v>1.103616694968274</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.28</v>
       </c>
       <c r="W19">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.17179926432069</v>
+        <v>9.301439701101559</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08367461437154353</v>
+        <v>0.08348627304862828</v>
       </c>
       <c r="C20">
-        <v>638.5286469522647</v>
+        <v>633.6525105895951</v>
       </c>
       <c r="D20">
-        <v>704.2086469522646</v>
+        <v>707.2925105895951</v>
       </c>
       <c r="E20">
-        <v>-25.12</v>
+        <v>-17.16</v>
       </c>
       <c r="F20">
-        <v>143.28</v>
+        <v>151.24</v>
       </c>
       <c r="G20">
         <v>77.59999999999999</v>
@@ -2933,28 +2933,28 @@
         <v>71.3</v>
       </c>
       <c r="M20">
-        <v>7.66548</v>
+        <v>8.091340000000001</v>
       </c>
       <c r="N20">
-        <v>63.63451999999999</v>
+        <v>63.20865999999999</v>
       </c>
       <c r="O20">
-        <v>17.8176656</v>
+        <v>17.6984248</v>
       </c>
       <c r="P20">
-        <v>45.8168544</v>
+        <v>45.5102352</v>
       </c>
       <c r="Q20">
-        <v>52.3168544</v>
+        <v>52.0102352</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09358660289212625</v>
+        <v>0.09403391734398553</v>
       </c>
       <c r="T20">
-        <v>1.103616694968274</v>
+        <v>1.113947282771029</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.301439701101561</v>
+        <v>8.811890243148847</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08348627304862828</v>
+        <v>0.08329793172571305</v>
       </c>
       <c r="C21">
-        <v>633.6525105895951</v>
+        <v>628.8035026786927</v>
       </c>
       <c r="D21">
-        <v>707.2925105895951</v>
+        <v>710.4035026786927</v>
       </c>
       <c r="E21">
-        <v>-17.16</v>
+        <v>-9.199999999999989</v>
       </c>
       <c r="F21">
-        <v>151.24</v>
+        <v>159.2</v>
       </c>
       <c r="G21">
         <v>77.59999999999999</v>
@@ -3015,28 +3015,28 @@
         <v>71.3</v>
       </c>
       <c r="M21">
-        <v>8.091340000000001</v>
+        <v>8.517200000000001</v>
       </c>
       <c r="N21">
-        <v>63.20865999999999</v>
+        <v>62.78279999999999</v>
       </c>
       <c r="O21">
-        <v>17.6984248</v>
+        <v>17.579184</v>
       </c>
       <c r="P21">
-        <v>45.5102352</v>
+        <v>45.203616</v>
       </c>
       <c r="Q21">
-        <v>52.0102352</v>
+        <v>51.703616</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09403391734398553</v>
+        <v>0.0944924146571413</v>
       </c>
       <c r="T21">
-        <v>1.113947282771029</v>
+        <v>1.124536135268852</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.811890243148847</v>
+        <v>8.371295730991404</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08329793172571305</v>
+        <v>0.08310959040279779</v>
       </c>
       <c r="C22">
-        <v>628.8035026786927</v>
+        <v>623.9819827705976</v>
       </c>
       <c r="D22">
-        <v>710.4035026786927</v>
+        <v>713.5419827705975</v>
       </c>
       <c r="E22">
-        <v>-9.199999999999989</v>
+        <v>-1.239999999999981</v>
       </c>
       <c r="F22">
-        <v>159.2</v>
+        <v>167.16</v>
       </c>
       <c r="G22">
         <v>77.59999999999999</v>
@@ -3097,28 +3097,28 @@
         <v>71.3</v>
       </c>
       <c r="M22">
-        <v>8.517200000000001</v>
+        <v>8.943060000000001</v>
       </c>
       <c r="N22">
-        <v>62.78279999999999</v>
+        <v>62.35693999999999</v>
       </c>
       <c r="O22">
-        <v>17.579184</v>
+        <v>17.4599432</v>
       </c>
       <c r="P22">
-        <v>45.203616</v>
+        <v>44.8969968</v>
       </c>
       <c r="Q22">
-        <v>51.703616</v>
+        <v>51.3969968</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0944924146571413</v>
+        <v>0.09496251949721239</v>
       </c>
       <c r="T22">
-        <v>1.124536135268852</v>
+        <v>1.135393059981811</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.371295730991404</v>
+        <v>7.972662600944195</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08310959040279779</v>
+        <v>0.08304796907988254</v>
       </c>
       <c r="C23">
-        <v>623.9819827705976</v>
+        <v>617.0548569393233</v>
       </c>
       <c r="D23">
-        <v>713.5419827705975</v>
+        <v>714.5748569393232</v>
       </c>
       <c r="E23">
-        <v>-1.240000000000009</v>
+        <v>6.719999999999999</v>
       </c>
       <c r="F23">
-        <v>167.16</v>
+        <v>175.12</v>
       </c>
       <c r="G23">
         <v>77.59999999999999</v>
@@ -3179,45 +3179,45 @@
         <v>71.3</v>
       </c>
       <c r="M23">
-        <v>8.943059999999999</v>
+        <v>9.509016000000001</v>
       </c>
       <c r="N23">
-        <v>62.35693999999999</v>
+        <v>61.79098399999999</v>
       </c>
       <c r="O23">
-        <v>17.4599432</v>
+        <v>17.30147552</v>
       </c>
       <c r="P23">
-        <v>44.8969968</v>
+        <v>44.48950848</v>
       </c>
       <c r="Q23">
-        <v>51.3969968</v>
+        <v>50.98950848</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09496251949721239</v>
+        <v>0.09544467830754172</v>
       </c>
       <c r="T23">
-        <v>1.135393059981811</v>
+        <v>1.146528367379716</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.28</v>
       </c>
       <c r="W23">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.972662600944196</v>
+        <v>7.498147021731795</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08304796907988254</v>
+        <v>0.08286538775696728</v>
       </c>
       <c r="C24">
-        <v>617.0548569393233</v>
+        <v>612.1728499620884</v>
       </c>
       <c r="D24">
-        <v>714.5748569393232</v>
+        <v>717.6528499620885</v>
       </c>
       <c r="E24">
-        <v>6.719999999999999</v>
+        <v>14.68000000000001</v>
       </c>
       <c r="F24">
-        <v>175.12</v>
+        <v>183.08</v>
       </c>
       <c r="G24">
         <v>77.59999999999999</v>
@@ -3261,28 +3261,28 @@
         <v>71.3</v>
       </c>
       <c r="M24">
-        <v>9.509016000000001</v>
+        <v>9.941244000000001</v>
       </c>
       <c r="N24">
-        <v>61.79098399999999</v>
+        <v>61.358756</v>
       </c>
       <c r="O24">
-        <v>17.30147552</v>
+        <v>17.18045168</v>
       </c>
       <c r="P24">
-        <v>44.48950848</v>
+        <v>44.17830432</v>
       </c>
       <c r="Q24">
-        <v>50.98950848</v>
+        <v>50.67830432</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09544467830754172</v>
+        <v>0.09593936072333413</v>
       </c>
       <c r="T24">
-        <v>1.146528367379716</v>
+        <v>1.157952903541204</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.498147021731795</v>
+        <v>7.172140629482588</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08286538775696728</v>
+        <v>0.08268280643405203</v>
       </c>
       <c r="C25">
-        <v>612.1728499620884</v>
+        <v>607.3174742787596</v>
       </c>
       <c r="D25">
-        <v>717.6528499620885</v>
+        <v>720.7574742787597</v>
       </c>
       <c r="E25">
-        <v>14.68000000000001</v>
+        <v>22.64000000000001</v>
       </c>
       <c r="F25">
-        <v>183.08</v>
+        <v>191.04</v>
       </c>
       <c r="G25">
         <v>77.59999999999999</v>
@@ -3343,28 +3343,28 @@
         <v>71.3</v>
       </c>
       <c r="M25">
-        <v>9.941244000000001</v>
+        <v>10.373472</v>
       </c>
       <c r="N25">
-        <v>61.358756</v>
+        <v>60.926528</v>
       </c>
       <c r="O25">
-        <v>17.18045168</v>
+        <v>17.05942784</v>
       </c>
       <c r="P25">
-        <v>44.17830432</v>
+        <v>43.86710015999999</v>
       </c>
       <c r="Q25">
-        <v>50.67830432</v>
+        <v>50.36710015999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09593936072333413</v>
+        <v>0.09644706109743689</v>
       </c>
       <c r="T25">
-        <v>1.157952903541204</v>
+        <v>1.169678085391152</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.172140629482588</v>
+        <v>6.873301436587479</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08268280643405203</v>
+        <v>0.08250022511113679</v>
       </c>
       <c r="C26">
-        <v>607.3174742787597</v>
+        <v>602.4890770184447</v>
       </c>
       <c r="D26">
-        <v>720.7574742787597</v>
+        <v>723.8890770184447</v>
       </c>
       <c r="E26">
-        <v>22.63999999999999</v>
+        <v>30.59999999999999</v>
       </c>
       <c r="F26">
-        <v>191.04</v>
+        <v>199</v>
       </c>
       <c r="G26">
         <v>77.59999999999999</v>
@@ -3425,28 +3425,28 @@
         <v>71.3</v>
       </c>
       <c r="M26">
-        <v>10.373472</v>
+        <v>10.8057</v>
       </c>
       <c r="N26">
-        <v>60.926528</v>
+        <v>60.4943</v>
       </c>
       <c r="O26">
-        <v>17.05942784</v>
+        <v>16.938404</v>
       </c>
       <c r="P26">
-        <v>43.86710015999999</v>
+        <v>43.55589599999999</v>
       </c>
       <c r="Q26">
-        <v>50.36710015999999</v>
+        <v>50.05589599999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09644706109743689</v>
+        <v>0.09696830014818238</v>
       </c>
       <c r="T26">
-        <v>1.169678085391152</v>
+        <v>1.181715938757099</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.87330143658748</v>
+        <v>6.59836937912398</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08250022511113679</v>
+        <v>0.08231764378822154</v>
       </c>
       <c r="C27">
-        <v>602.4890770184447</v>
+        <v>597.6880113695117</v>
       </c>
       <c r="D27">
-        <v>723.8890770184447</v>
+        <v>727.0480113695118</v>
       </c>
       <c r="E27">
-        <v>30.59999999999999</v>
+        <v>38.56</v>
       </c>
       <c r="F27">
-        <v>199</v>
+        <v>206.96</v>
       </c>
       <c r="G27">
         <v>77.59999999999999</v>
@@ -3507,28 +3507,28 @@
         <v>71.3</v>
       </c>
       <c r="M27">
-        <v>10.8057</v>
+        <v>11.237928</v>
       </c>
       <c r="N27">
-        <v>60.4943</v>
+        <v>60.062072</v>
       </c>
       <c r="O27">
-        <v>16.938404</v>
+        <v>16.81738016</v>
       </c>
       <c r="P27">
-        <v>43.55589599999999</v>
+        <v>43.24469184</v>
       </c>
       <c r="Q27">
-        <v>50.05589599999999</v>
+        <v>49.74469184</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09696830014818238</v>
+        <v>0.09750362674083991</v>
       </c>
       <c r="T27">
-        <v>1.181715938757099</v>
+        <v>1.194079139511314</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.59836937912398</v>
+        <v>6.344585941465366</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08231764378822154</v>
+        <v>0.08232946246530629</v>
       </c>
       <c r="C28">
-        <v>597.6880113695117</v>
+        <v>589.5226959697918</v>
       </c>
       <c r="D28">
-        <v>727.0480113695118</v>
+        <v>726.8426959697917</v>
       </c>
       <c r="E28">
-        <v>38.56</v>
+        <v>46.52000000000001</v>
       </c>
       <c r="F28">
-        <v>206.96</v>
+        <v>214.92</v>
       </c>
       <c r="G28">
         <v>77.59999999999999</v>
@@ -3589,45 +3589,45 @@
         <v>71.3</v>
       </c>
       <c r="M28">
-        <v>11.237928</v>
+        <v>11.885076</v>
       </c>
       <c r="N28">
-        <v>60.062072</v>
+        <v>59.414924</v>
       </c>
       <c r="O28">
-        <v>16.81738016</v>
+        <v>16.63617872</v>
       </c>
       <c r="P28">
-        <v>43.24469184</v>
+        <v>42.77874528</v>
       </c>
       <c r="Q28">
-        <v>49.74469184</v>
+        <v>49.27874528</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09750362674083991</v>
+        <v>0.09805361981548806</v>
       </c>
       <c r="T28">
-        <v>1.194079139511314</v>
+        <v>1.206781058094412</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.344585941465366</v>
+        <v>5.999120241216799</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08232946246530629</v>
+        <v>0.08215408114239103</v>
       </c>
       <c r="C29">
-        <v>589.5226959697918</v>
+        <v>584.6213975261934</v>
       </c>
       <c r="D29">
-        <v>726.8426959697917</v>
+        <v>729.9013975261934</v>
       </c>
       <c r="E29">
-        <v>46.52000000000001</v>
+        <v>54.48000000000002</v>
       </c>
       <c r="F29">
-        <v>214.92</v>
+        <v>222.88</v>
       </c>
       <c r="G29">
         <v>77.59999999999999</v>
@@ -3671,28 +3671,28 @@
         <v>71.3</v>
       </c>
       <c r="M29">
-        <v>11.885076</v>
+        <v>12.325264</v>
       </c>
       <c r="N29">
-        <v>59.414924</v>
+        <v>58.97473599999999</v>
       </c>
       <c r="O29">
-        <v>16.63617872</v>
+        <v>16.51292608</v>
       </c>
       <c r="P29">
-        <v>42.77874528</v>
+        <v>42.46180991999999</v>
       </c>
       <c r="Q29">
-        <v>49.27874528</v>
+        <v>48.96180991999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09805361981548806</v>
+        <v>0.09861889047554311</v>
       </c>
       <c r="T29">
-        <v>1.206781058094412</v>
+        <v>1.219835807749263</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.999120241216799</v>
+        <v>5.784865946887627</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08215408114239103</v>
+        <v>0.08197869981947577</v>
       </c>
       <c r="C30">
-        <v>584.6213975261934</v>
+        <v>579.7459511469772</v>
       </c>
       <c r="D30">
-        <v>729.9013975261934</v>
+        <v>732.9859511469772</v>
       </c>
       <c r="E30">
-        <v>54.48000000000002</v>
+        <v>62.44000000000003</v>
       </c>
       <c r="F30">
-        <v>222.88</v>
+        <v>230.84</v>
       </c>
       <c r="G30">
         <v>77.59999999999999</v>
@@ -3753,28 +3753,28 @@
         <v>71.3</v>
       </c>
       <c r="M30">
-        <v>12.325264</v>
+        <v>12.765452</v>
       </c>
       <c r="N30">
-        <v>58.97473599999999</v>
+        <v>58.53454799999999</v>
       </c>
       <c r="O30">
-        <v>16.51292608</v>
+        <v>16.38967344</v>
       </c>
       <c r="P30">
-        <v>42.46180991999999</v>
+        <v>42.14487455999999</v>
       </c>
       <c r="Q30">
-        <v>48.96180991999999</v>
+        <v>48.64487455999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09861889047554311</v>
+        <v>0.09920008425278279</v>
       </c>
       <c r="T30">
-        <v>1.219835807749263</v>
+        <v>1.233258296831012</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.784865946887627</v>
+        <v>5.585387810788054</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08197869981947577</v>
+        <v>0.08180331849656053</v>
       </c>
       <c r="C31">
-        <v>579.7459511469772</v>
+        <v>574.8966859745371</v>
       </c>
       <c r="D31">
-        <v>732.9859511469772</v>
+        <v>736.0966859745371</v>
       </c>
       <c r="E31">
-        <v>62.43999999999997</v>
+        <v>70.39999999999998</v>
       </c>
       <c r="F31">
-        <v>230.84</v>
+        <v>238.8</v>
       </c>
       <c r="G31">
         <v>77.59999999999999</v>
@@ -3835,28 +3835,28 @@
         <v>71.3</v>
       </c>
       <c r="M31">
-        <v>12.765452</v>
+        <v>13.20564</v>
       </c>
       <c r="N31">
-        <v>58.534548</v>
+        <v>58.09435999999999</v>
       </c>
       <c r="O31">
-        <v>16.38967344</v>
+        <v>16.2664208</v>
       </c>
       <c r="P31">
-        <v>42.14487456</v>
+        <v>41.8279392</v>
       </c>
       <c r="Q31">
-        <v>48.64487456</v>
+        <v>48.3279392</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09920008425278279</v>
+        <v>0.09979788356651506</v>
       </c>
       <c r="T31">
-        <v>1.233258296831012</v>
+        <v>1.24706428560081</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.585387810788055</v>
+        <v>5.39920821709512</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08180331849656053</v>
+        <v>0.08162793717364528</v>
       </c>
       <c r="C32">
-        <v>574.8966859745371</v>
+        <v>570.0739367624999</v>
       </c>
       <c r="D32">
-        <v>736.0966859745371</v>
+        <v>739.2339367624999</v>
       </c>
       <c r="E32">
-        <v>70.39999999999998</v>
+        <v>78.35999999999999</v>
       </c>
       <c r="F32">
-        <v>238.8</v>
+        <v>246.76</v>
       </c>
       <c r="G32">
         <v>77.59999999999999</v>
@@ -3917,28 +3917,28 @@
         <v>71.3</v>
       </c>
       <c r="M32">
-        <v>13.20564</v>
+        <v>13.645828</v>
       </c>
       <c r="N32">
-        <v>58.09435999999999</v>
+        <v>57.654172</v>
       </c>
       <c r="O32">
-        <v>16.2664208</v>
+        <v>16.14316816</v>
       </c>
       <c r="P32">
-        <v>41.8279392</v>
+        <v>41.51100383999999</v>
       </c>
       <c r="Q32">
-        <v>48.3279392</v>
+        <v>48.01100383999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09979788356651506</v>
+        <v>0.1004130103965874</v>
       </c>
       <c r="T32">
-        <v>1.24706428560081</v>
+        <v>1.261270447958138</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.39920821709512</v>
+        <v>5.225040210092051</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08162793717364528</v>
+        <v>0.08145255585073001</v>
       </c>
       <c r="C33">
-        <v>570.0739367624999</v>
+        <v>565.2780439958105</v>
       </c>
       <c r="D33">
-        <v>739.2339367624999</v>
+        <v>742.3980439958106</v>
       </c>
       <c r="E33">
-        <v>78.35999999999999</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="F33">
-        <v>246.76</v>
+        <v>254.72</v>
       </c>
       <c r="G33">
         <v>77.59999999999999</v>
@@ -3999,28 +3999,28 @@
         <v>71.3</v>
       </c>
       <c r="M33">
-        <v>13.645828</v>
+        <v>14.086016</v>
       </c>
       <c r="N33">
-        <v>57.654172</v>
+        <v>57.213984</v>
       </c>
       <c r="O33">
-        <v>16.14316816</v>
+        <v>16.01991552</v>
       </c>
       <c r="P33">
-        <v>41.51100383999999</v>
+        <v>41.19406848</v>
       </c>
       <c r="Q33">
-        <v>48.01100383999999</v>
+        <v>47.69406848</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1004130103965874</v>
+        <v>0.10104622919225</v>
       </c>
       <c r="T33">
-        <v>1.261270447958138</v>
+        <v>1.275894438620093</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.225040210092051</v>
+        <v>5.061757703526674</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08145255585073001</v>
+        <v>0.08127717452781477</v>
       </c>
       <c r="C34">
-        <v>565.2780439958105</v>
+        <v>560.5093540139173</v>
       </c>
       <c r="D34">
-        <v>742.3980439958106</v>
+        <v>745.5893540139173</v>
       </c>
       <c r="E34">
-        <v>86.31999999999999</v>
+        <v>94.28</v>
       </c>
       <c r="F34">
-        <v>254.72</v>
+        <v>262.68</v>
       </c>
       <c r="G34">
         <v>77.59999999999999</v>
@@ -4081,28 +4081,28 @@
         <v>71.3</v>
       </c>
       <c r="M34">
-        <v>14.086016</v>
+        <v>14.526204</v>
       </c>
       <c r="N34">
-        <v>57.213984</v>
+        <v>56.773796</v>
       </c>
       <c r="O34">
-        <v>16.01991552</v>
+        <v>15.89666288</v>
       </c>
       <c r="P34">
-        <v>41.19406848</v>
+        <v>40.87713312</v>
       </c>
       <c r="Q34">
-        <v>47.69406848</v>
+        <v>47.37713312</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.10104622919225</v>
+        <v>0.1016983500415146</v>
       </c>
       <c r="T34">
-        <v>1.275894438620093</v>
+        <v>1.290954966316734</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.061757703526674</v>
+        <v>4.908371106450108</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08127717452781477</v>
+        <v>0.08110179320489953</v>
       </c>
       <c r="C35">
-        <v>560.5093540139173</v>
+        <v>555.768219137148</v>
       </c>
       <c r="D35">
-        <v>745.5893540139173</v>
+        <v>748.8082191371481</v>
       </c>
       <c r="E35">
-        <v>94.28</v>
+        <v>102.24</v>
       </c>
       <c r="F35">
-        <v>262.68</v>
+        <v>270.64</v>
       </c>
       <c r="G35">
         <v>77.59999999999999</v>
@@ -4163,28 +4163,28 @@
         <v>71.3</v>
       </c>
       <c r="M35">
-        <v>14.526204</v>
+        <v>14.966392</v>
       </c>
       <c r="N35">
-        <v>56.773796</v>
+        <v>56.333608</v>
       </c>
       <c r="O35">
-        <v>15.89666288</v>
+        <v>15.77341024</v>
       </c>
       <c r="P35">
-        <v>40.87713312</v>
+        <v>40.56019775999999</v>
       </c>
       <c r="Q35">
-        <v>47.37713312</v>
+        <v>47.06019775999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1016983500415146</v>
+        <v>0.1023702321286357</v>
       </c>
       <c r="T35">
-        <v>1.290954966316734</v>
+        <v>1.306471873640547</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.908371106450108</v>
+        <v>4.764007250378047</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08110179320489953</v>
+        <v>0.08092641188198428</v>
       </c>
       <c r="C36">
-        <v>555.768219137148</v>
+        <v>551.054997796374</v>
       </c>
       <c r="D36">
-        <v>748.8082191371481</v>
+        <v>752.054997796374</v>
       </c>
       <c r="E36">
-        <v>102.24</v>
+        <v>110.2</v>
       </c>
       <c r="F36">
-        <v>270.64</v>
+        <v>278.6</v>
       </c>
       <c r="G36">
         <v>77.59999999999999</v>
@@ -4245,28 +4245,28 @@
         <v>71.3</v>
       </c>
       <c r="M36">
-        <v>14.966392</v>
+        <v>15.40658</v>
       </c>
       <c r="N36">
-        <v>56.333608</v>
+        <v>55.89341999999999</v>
       </c>
       <c r="O36">
-        <v>15.77341024</v>
+        <v>15.6501576</v>
       </c>
       <c r="P36">
-        <v>40.56019775999999</v>
+        <v>40.24326239999999</v>
       </c>
       <c r="Q36">
-        <v>47.06019775999999</v>
+        <v>46.74326239999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1023702321286357</v>
+        <v>0.103062787510745</v>
       </c>
       <c r="T36">
-        <v>1.306471873640547</v>
+        <v>1.322466224266629</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.764007250378047</v>
+        <v>4.627892757510102</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08092641188198428</v>
+        <v>0.08139903055906901</v>
       </c>
       <c r="C37">
-        <v>551.054997796374</v>
+        <v>534.4091116975882</v>
       </c>
       <c r="D37">
-        <v>752.054997796374</v>
+        <v>743.3691116975882</v>
       </c>
       <c r="E37">
-        <v>110.2</v>
+        <v>118.1600000000001</v>
       </c>
       <c r="F37">
-        <v>278.6</v>
+        <v>286.5600000000001</v>
       </c>
       <c r="G37">
         <v>77.59999999999999</v>
@@ -4327,45 +4327,45 @@
         <v>71.3</v>
       </c>
       <c r="M37">
-        <v>15.40658</v>
+        <v>16.563168</v>
       </c>
       <c r="N37">
-        <v>55.89341999999999</v>
+        <v>54.73683199999999</v>
       </c>
       <c r="O37">
-        <v>15.6501576</v>
+        <v>15.32631296</v>
       </c>
       <c r="P37">
-        <v>40.24326239999999</v>
+        <v>39.41051904</v>
       </c>
       <c r="Q37">
-        <v>46.74326239999999</v>
+        <v>45.91051904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.103062787510745</v>
+        <v>0.1037769852485454</v>
       </c>
       <c r="T37">
-        <v>1.322466224266629</v>
+        <v>1.338960398349777</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.28</v>
       </c>
       <c r="W37">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.627892757510102</v>
+        <v>4.30473204159977</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08139903055906902</v>
+        <v>0.08124164923615378</v>
       </c>
       <c r="C38">
-        <v>534.4091116975878</v>
+        <v>529.3191312700893</v>
       </c>
       <c r="D38">
-        <v>743.3691116975879</v>
+        <v>746.2391312700893</v>
       </c>
       <c r="E38">
-        <v>118.16</v>
+        <v>126.12</v>
       </c>
       <c r="F38">
-        <v>286.56</v>
+        <v>294.52</v>
       </c>
       <c r="G38">
         <v>77.59999999999999</v>
@@ -4409,28 +4409,28 @@
         <v>71.3</v>
       </c>
       <c r="M38">
-        <v>16.563168</v>
+        <v>17.023256</v>
       </c>
       <c r="N38">
-        <v>54.73683199999999</v>
+        <v>54.27674399999999</v>
       </c>
       <c r="O38">
-        <v>15.32631296</v>
+        <v>15.19748832</v>
       </c>
       <c r="P38">
-        <v>39.41051904</v>
+        <v>39.07925568</v>
       </c>
       <c r="Q38">
-        <v>45.91051904</v>
+        <v>45.57925568</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1037769852485454</v>
+        <v>0.1045138559304028</v>
       </c>
       <c r="T38">
-        <v>1.338960398349777</v>
+        <v>1.355978197006994</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.30473204159977</v>
+        <v>4.188387932367345</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08124164923615378</v>
+        <v>0.08108426791323853</v>
       </c>
       <c r="C39">
-        <v>529.3191312700893</v>
+        <v>524.25139803353</v>
       </c>
       <c r="D39">
-        <v>746.2391312700893</v>
+        <v>749.13139803353</v>
       </c>
       <c r="E39">
-        <v>126.12</v>
+        <v>134.08</v>
       </c>
       <c r="F39">
-        <v>294.52</v>
+        <v>302.48</v>
       </c>
       <c r="G39">
         <v>77.59999999999999</v>
@@ -4491,28 +4491,28 @@
         <v>71.3</v>
       </c>
       <c r="M39">
-        <v>17.023256</v>
+        <v>17.483344</v>
       </c>
       <c r="N39">
-        <v>54.27674399999999</v>
+        <v>53.81665599999999</v>
       </c>
       <c r="O39">
-        <v>15.19748832</v>
+        <v>15.06866368</v>
       </c>
       <c r="P39">
-        <v>39.07925568</v>
+        <v>38.74799231999999</v>
       </c>
       <c r="Q39">
-        <v>45.57925568</v>
+        <v>45.24799231999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1045138559304028</v>
+        <v>0.1052744966342557</v>
       </c>
       <c r="T39">
-        <v>1.355978197006994</v>
+        <v>1.373544956911217</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.188387932367345</v>
+        <v>4.078167197305046</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08108426791323853</v>
+        <v>0.08190968659032327</v>
       </c>
       <c r="C40">
-        <v>524.25139803353</v>
+        <v>501.3668947241894</v>
       </c>
       <c r="D40">
-        <v>749.13139803353</v>
+        <v>734.2068947241894</v>
       </c>
       <c r="E40">
-        <v>134.08</v>
+        <v>142.04</v>
       </c>
       <c r="F40">
-        <v>302.48</v>
+        <v>310.44</v>
       </c>
       <c r="G40">
         <v>77.59999999999999</v>
@@ -4573,45 +4573,45 @@
         <v>71.3</v>
       </c>
       <c r="M40">
-        <v>17.483344</v>
+        <v>19.029972</v>
       </c>
       <c r="N40">
-        <v>53.81665599999999</v>
+        <v>52.270028</v>
       </c>
       <c r="O40">
-        <v>15.06866368</v>
+        <v>14.63560784</v>
       </c>
       <c r="P40">
-        <v>38.74799231999999</v>
+        <v>37.63442016</v>
       </c>
       <c r="Q40">
-        <v>45.24799231999999</v>
+        <v>44.13442016</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1052744966342557</v>
+        <v>0.1060600763775791</v>
       </c>
       <c r="T40">
-        <v>1.373544956911217</v>
+        <v>1.391687676156562</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.28</v>
       </c>
       <c r="W40">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.078167197305046</v>
+        <v>3.746721224813153</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08190968659032327</v>
+        <v>0.08177750526740803</v>
       </c>
       <c r="C41">
-        <v>501.3668947241894</v>
+        <v>495.7567651313786</v>
       </c>
       <c r="D41">
-        <v>734.2068947241894</v>
+        <v>736.5567651313786</v>
       </c>
       <c r="E41">
-        <v>142.04</v>
+        <v>150</v>
       </c>
       <c r="F41">
-        <v>310.44</v>
+        <v>318.4</v>
       </c>
       <c r="G41">
         <v>77.59999999999999</v>
@@ -4655,28 +4655,28 @@
         <v>71.3</v>
       </c>
       <c r="M41">
-        <v>19.029972</v>
+        <v>19.51792</v>
       </c>
       <c r="N41">
-        <v>52.270028</v>
+        <v>51.78207999999999</v>
       </c>
       <c r="O41">
-        <v>14.63560784</v>
+        <v>14.4989824</v>
       </c>
       <c r="P41">
-        <v>37.63442016</v>
+        <v>37.28309759999999</v>
       </c>
       <c r="Q41">
-        <v>44.13442016</v>
+        <v>43.78309759999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1060600763775791</v>
+        <v>0.1068718421123467</v>
       </c>
       <c r="T41">
-        <v>1.391687676156562</v>
+        <v>1.410435152710086</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.746721224813153</v>
+        <v>3.653053194192823</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08177750526740803</v>
+        <v>0.08164532394449277</v>
       </c>
       <c r="C42">
-        <v>495.7567651313786</v>
+        <v>490.1617256196828</v>
       </c>
       <c r="D42">
-        <v>736.5567651313786</v>
+        <v>738.9217256196828</v>
       </c>
       <c r="E42">
-        <v>150</v>
+        <v>157.96</v>
       </c>
       <c r="F42">
-        <v>318.4</v>
+        <v>326.36</v>
       </c>
       <c r="G42">
         <v>77.59999999999999</v>
@@ -4737,28 +4737,28 @@
         <v>71.3</v>
       </c>
       <c r="M42">
-        <v>19.51792</v>
+        <v>20.005868</v>
       </c>
       <c r="N42">
-        <v>51.78207999999999</v>
+        <v>51.294132</v>
       </c>
       <c r="O42">
-        <v>14.4989824</v>
+        <v>14.36235696</v>
       </c>
       <c r="P42">
-        <v>37.28309759999999</v>
+        <v>36.93177504</v>
       </c>
       <c r="Q42">
-        <v>43.78309759999999</v>
+        <v>43.43177504</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1068718421123467</v>
+        <v>0.1077111253296488</v>
       </c>
       <c r="T42">
-        <v>1.410435152710086</v>
+        <v>1.42981813694339</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.653053194192823</v>
+        <v>3.563954335797877</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08164532394449277</v>
+        <v>0.08235986262157752</v>
       </c>
       <c r="C43">
-        <v>490.1617256196828</v>
+        <v>469.5951133689665</v>
       </c>
       <c r="D43">
-        <v>738.9217256196828</v>
+        <v>726.3151133689665</v>
       </c>
       <c r="E43">
-        <v>157.96</v>
+        <v>165.92</v>
       </c>
       <c r="F43">
-        <v>326.36</v>
+        <v>334.3200000000001</v>
       </c>
       <c r="G43">
         <v>77.59999999999999</v>
@@ -4819,45 +4819,45 @@
         <v>71.3</v>
       </c>
       <c r="M43">
-        <v>20.005868</v>
+        <v>21.42991200000001</v>
       </c>
       <c r="N43">
-        <v>51.294132</v>
+        <v>49.870088</v>
       </c>
       <c r="O43">
-        <v>14.36235696</v>
+        <v>13.96362464</v>
       </c>
       <c r="P43">
-        <v>36.93177504</v>
+        <v>35.90646336</v>
       </c>
       <c r="Q43">
-        <v>43.43177504</v>
+        <v>42.40646336</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1077111253296488</v>
+        <v>0.1085793493475475</v>
       </c>
       <c r="T43">
-        <v>1.42981813694339</v>
+        <v>1.449869499943359</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.28</v>
       </c>
       <c r="W43">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.563954335797877</v>
+        <v>3.327125188381547</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08235986262157753</v>
+        <v>0.08224784129866228</v>
       </c>
       <c r="C44">
-        <v>469.5951133689662</v>
+        <v>463.5829976790143</v>
       </c>
       <c r="D44">
-        <v>726.3151133689662</v>
+        <v>728.2629976790142</v>
       </c>
       <c r="E44">
-        <v>165.92</v>
+        <v>173.88</v>
       </c>
       <c r="F44">
-        <v>334.32</v>
+        <v>342.28</v>
       </c>
       <c r="G44">
         <v>77.59999999999999</v>
@@ -4901,28 +4901,28 @@
         <v>71.3</v>
       </c>
       <c r="M44">
-        <v>21.429912</v>
+        <v>21.940148</v>
       </c>
       <c r="N44">
-        <v>49.870088</v>
+        <v>49.359852</v>
       </c>
       <c r="O44">
-        <v>13.96362464</v>
+        <v>13.82075856</v>
       </c>
       <c r="P44">
-        <v>35.90646336</v>
+        <v>35.53909343999999</v>
       </c>
       <c r="Q44">
-        <v>42.40646336</v>
+        <v>42.03909343999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1085793493475475</v>
+        <v>0.1094780373660742</v>
       </c>
       <c r="T44">
-        <v>1.449869499943359</v>
+        <v>1.470624419539819</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.327125188381548</v>
+        <v>3.249750184000582</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08224784129866228</v>
+        <v>0.08213581997574702</v>
       </c>
       <c r="C45">
-        <v>463.5829976790143</v>
+        <v>457.5813580380416</v>
       </c>
       <c r="D45">
-        <v>728.2629976790142</v>
+        <v>730.2213580380416</v>
       </c>
       <c r="E45">
-        <v>173.88</v>
+        <v>181.84</v>
       </c>
       <c r="F45">
-        <v>342.28</v>
+        <v>350.24</v>
       </c>
       <c r="G45">
         <v>77.59999999999999</v>
@@ -4983,28 +4983,28 @@
         <v>71.3</v>
       </c>
       <c r="M45">
-        <v>21.940148</v>
+        <v>22.450384</v>
       </c>
       <c r="N45">
-        <v>49.359852</v>
+        <v>48.849616</v>
       </c>
       <c r="O45">
-        <v>13.82075856</v>
+        <v>13.67789248</v>
       </c>
       <c r="P45">
-        <v>35.53909343999999</v>
+        <v>35.17172352</v>
       </c>
       <c r="Q45">
-        <v>42.03909343999999</v>
+        <v>41.67172352</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1094780373660742</v>
+        <v>0.1104088213852625</v>
       </c>
       <c r="T45">
-        <v>1.470624419539819</v>
+        <v>1.492120586264724</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.249750184000582</v>
+        <v>3.175892225273296</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08213581997574702</v>
+        <v>0.08202379865283177</v>
       </c>
       <c r="C46">
-        <v>457.5813580380416</v>
+        <v>451.5902791868497</v>
       </c>
       <c r="D46">
-        <v>730.2213580380416</v>
+        <v>732.1902791868497</v>
       </c>
       <c r="E46">
-        <v>181.84</v>
+        <v>189.8</v>
       </c>
       <c r="F46">
-        <v>350.24</v>
+        <v>358.2</v>
       </c>
       <c r="G46">
         <v>77.59999999999999</v>
@@ -5065,28 +5065,28 @@
         <v>71.3</v>
       </c>
       <c r="M46">
-        <v>22.450384</v>
+        <v>22.96062</v>
       </c>
       <c r="N46">
-        <v>48.849616</v>
+        <v>48.33937999999999</v>
       </c>
       <c r="O46">
-        <v>13.67789248</v>
+        <v>13.5350264</v>
       </c>
       <c r="P46">
-        <v>35.17172352</v>
+        <v>34.80435359999999</v>
       </c>
       <c r="Q46">
-        <v>41.67172352</v>
+        <v>41.30435359999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1104088213852625</v>
+        <v>0.1113734520960578</v>
       </c>
       <c r="T46">
-        <v>1.492120586264724</v>
+        <v>1.514398431779625</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.175892225273296</v>
+        <v>3.105316842489444</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08202379865283177</v>
+        <v>0.08191177732991653</v>
       </c>
       <c r="C47">
-        <v>451.5902791868497</v>
+        <v>445.6098467826693</v>
       </c>
       <c r="D47">
-        <v>732.1902791868497</v>
+        <v>734.1698467826693</v>
       </c>
       <c r="E47">
-        <v>189.8</v>
+        <v>197.76</v>
       </c>
       <c r="F47">
-        <v>358.2</v>
+        <v>366.16</v>
       </c>
       <c r="G47">
         <v>77.59999999999999</v>
@@ -5147,28 +5147,28 @@
         <v>71.3</v>
       </c>
       <c r="M47">
-        <v>22.96062</v>
+        <v>23.470856</v>
       </c>
       <c r="N47">
-        <v>48.33937999999999</v>
+        <v>47.82914399999999</v>
       </c>
       <c r="O47">
-        <v>13.5350264</v>
+        <v>13.39216032</v>
       </c>
       <c r="P47">
-        <v>34.80435359999999</v>
+        <v>34.43698368</v>
       </c>
       <c r="Q47">
-        <v>41.30435359999999</v>
+        <v>40.93698368</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1113734520960578</v>
+        <v>0.1123738098702158</v>
       </c>
       <c r="T47">
-        <v>1.514398431779625</v>
+        <v>1.537501382683967</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.105316842489444</v>
+        <v>3.037809954609239</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08191177732991653</v>
+        <v>0.08443927600700128</v>
       </c>
       <c r="C48">
-        <v>445.6098467826693</v>
+        <v>395.4396490247311</v>
       </c>
       <c r="D48">
-        <v>734.1698467826693</v>
+        <v>691.9596490247311</v>
       </c>
       <c r="E48">
-        <v>197.76</v>
+        <v>205.72</v>
       </c>
       <c r="F48">
-        <v>366.16</v>
+        <v>374.12</v>
       </c>
       <c r="G48">
         <v>77.59999999999999</v>
@@ -5229,45 +5229,45 @@
         <v>71.3</v>
       </c>
       <c r="M48">
-        <v>23.470856</v>
+        <v>26.899228</v>
       </c>
       <c r="N48">
-        <v>47.82914399999999</v>
+        <v>44.400772</v>
       </c>
       <c r="O48">
-        <v>13.39216032</v>
+        <v>12.43221616</v>
       </c>
       <c r="P48">
-        <v>34.43698368</v>
+        <v>31.96855584</v>
       </c>
       <c r="Q48">
-        <v>40.93698368</v>
+        <v>38.46855583999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1123738098702158</v>
+        <v>0.113411916994342</v>
       </c>
       <c r="T48">
-        <v>1.537501382683967</v>
+        <v>1.561476143056398</v>
       </c>
       <c r="U48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.28</v>
       </c>
       <c r="W48">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.037809954609239</v>
+        <v>2.65063369104868</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08443927600700128</v>
+        <v>0.08438341468408603</v>
       </c>
       <c r="C49">
-        <v>395.4396490247311</v>
+        <v>388.3600369938114</v>
       </c>
       <c r="D49">
-        <v>691.9596490247311</v>
+        <v>692.8400369938114</v>
       </c>
       <c r="E49">
-        <v>205.72</v>
+        <v>213.68</v>
       </c>
       <c r="F49">
-        <v>374.12</v>
+        <v>382.08</v>
       </c>
       <c r="G49">
         <v>77.59999999999999</v>
@@ -5311,28 +5311,28 @@
         <v>71.3</v>
       </c>
       <c r="M49">
-        <v>26.899228</v>
+        <v>27.47155200000001</v>
       </c>
       <c r="N49">
-        <v>44.400772</v>
+        <v>43.82844799999999</v>
       </c>
       <c r="O49">
-        <v>12.43221616</v>
+        <v>12.27196544</v>
       </c>
       <c r="P49">
-        <v>31.96855584</v>
+        <v>31.55648256</v>
       </c>
       <c r="Q49">
-        <v>38.46855583999999</v>
+        <v>38.05648255999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.113411916994342</v>
+        <v>0.11448995131555</v>
       </c>
       <c r="T49">
-        <v>1.561476143056398</v>
+        <v>1.586373009596999</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.65063369104868</v>
+        <v>2.595412155818499</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08438341468408603</v>
+        <v>0.08432755336117077</v>
       </c>
       <c r="C50">
-        <v>388.3600369938114</v>
+        <v>381.282668071663</v>
       </c>
       <c r="D50">
-        <v>692.8400369938114</v>
+        <v>693.722668071663</v>
       </c>
       <c r="E50">
-        <v>213.68</v>
+        <v>221.64</v>
       </c>
       <c r="F50">
-        <v>382.08</v>
+        <v>390.04</v>
       </c>
       <c r="G50">
         <v>77.59999999999999</v>
@@ -5393,28 +5393,28 @@
         <v>71.3</v>
       </c>
       <c r="M50">
-        <v>27.471552</v>
+        <v>28.043876</v>
       </c>
       <c r="N50">
-        <v>43.82844799999999</v>
+        <v>43.25612399999999</v>
       </c>
       <c r="O50">
-        <v>12.27196544</v>
+        <v>12.11171472</v>
       </c>
       <c r="P50">
-        <v>31.55648256</v>
+        <v>31.14440927999999</v>
       </c>
       <c r="Q50">
-        <v>38.05648255999999</v>
+        <v>37.64440927999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.11448995131555</v>
+        <v>0.1156102614924917</v>
       </c>
       <c r="T50">
-        <v>1.586373009596999</v>
+        <v>1.612246223845074</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.595412155818499</v>
+        <v>2.542444560801794</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08432755336117077</v>
+        <v>0.08567569203825551</v>
       </c>
       <c r="C51">
-        <v>381.282668071663</v>
+        <v>352.6305767645173</v>
       </c>
       <c r="D51">
-        <v>693.722668071663</v>
+        <v>673.0305767645173</v>
       </c>
       <c r="E51">
-        <v>221.64</v>
+        <v>229.6</v>
       </c>
       <c r="F51">
-        <v>390.04</v>
+        <v>398</v>
       </c>
       <c r="G51">
         <v>77.59999999999999</v>
@@ -5475,45 +5475,45 @@
         <v>71.3</v>
       </c>
       <c r="M51">
-        <v>28.043876</v>
+        <v>30.1684</v>
       </c>
       <c r="N51">
-        <v>43.25612399999999</v>
+        <v>41.13159999999999</v>
       </c>
       <c r="O51">
-        <v>12.11171472</v>
+        <v>11.516848</v>
       </c>
       <c r="P51">
-        <v>31.14440927999999</v>
+        <v>29.61475199999999</v>
       </c>
       <c r="Q51">
-        <v>37.64440927999999</v>
+        <v>36.114752</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1156102614924917</v>
+        <v>0.116775384076511</v>
       </c>
       <c r="T51">
-        <v>1.612246223845074</v>
+        <v>1.639154366663073</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.28</v>
       </c>
       <c r="W51">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.542444560801794</v>
+        <v>2.363400114026597</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08567569203825551</v>
+        <v>0.08564791071534027</v>
       </c>
       <c r="C52">
-        <v>352.6305767645173</v>
+        <v>345.0845179855955</v>
       </c>
       <c r="D52">
-        <v>673.0305767645173</v>
+        <v>673.4445179855954</v>
       </c>
       <c r="E52">
-        <v>229.6</v>
+        <v>237.56</v>
       </c>
       <c r="F52">
-        <v>398</v>
+        <v>405.96</v>
       </c>
       <c r="G52">
         <v>77.59999999999999</v>
@@ -5557,28 +5557,28 @@
         <v>71.3</v>
       </c>
       <c r="M52">
-        <v>30.1684</v>
+        <v>30.771768</v>
       </c>
       <c r="N52">
-        <v>41.13159999999999</v>
+        <v>40.528232</v>
       </c>
       <c r="O52">
-        <v>11.516848</v>
+        <v>11.34790496</v>
       </c>
       <c r="P52">
-        <v>29.61475199999999</v>
+        <v>29.18032703999999</v>
       </c>
       <c r="Q52">
-        <v>36.114752</v>
+        <v>35.68032703999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.116775384076511</v>
+        <v>0.1179880626843679</v>
       </c>
       <c r="T52">
-        <v>1.639154366663073</v>
+        <v>1.667160801024663</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.363400114026597</v>
+        <v>2.317058935320193</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08564791071534027</v>
+        <v>0.08562012939242503</v>
       </c>
       <c r="C53">
-        <v>345.0845179855955</v>
+        <v>337.53896870146</v>
       </c>
       <c r="D53">
-        <v>673.4445179855954</v>
+        <v>673.85896870146</v>
       </c>
       <c r="E53">
-        <v>237.56</v>
+        <v>245.52</v>
       </c>
       <c r="F53">
-        <v>405.96</v>
+        <v>413.92</v>
       </c>
       <c r="G53">
         <v>77.59999999999999</v>
@@ -5639,28 +5639,28 @@
         <v>71.3</v>
       </c>
       <c r="M53">
-        <v>30.771768</v>
+        <v>31.375136</v>
       </c>
       <c r="N53">
-        <v>40.528232</v>
+        <v>39.92486399999999</v>
       </c>
       <c r="O53">
-        <v>11.34790496</v>
+        <v>11.17896192</v>
       </c>
       <c r="P53">
-        <v>29.18032703999999</v>
+        <v>28.74590207999999</v>
       </c>
       <c r="Q53">
-        <v>35.68032703999999</v>
+        <v>35.24590207999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1179880626843679</v>
+        <v>0.1192512695675521</v>
       </c>
       <c r="T53">
-        <v>1.667160801024663</v>
+        <v>1.696334170151319</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.317058935320193</v>
+        <v>2.272500109640958</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08562012939242503</v>
+        <v>0.08559234806950977</v>
       </c>
       <c r="C54">
-        <v>337.53896870146</v>
+        <v>329.9939298533488</v>
       </c>
       <c r="D54">
-        <v>673.85896870146</v>
+        <v>674.2739298533488</v>
       </c>
       <c r="E54">
-        <v>245.52</v>
+        <v>253.48</v>
       </c>
       <c r="F54">
-        <v>413.92</v>
+        <v>421.88</v>
       </c>
       <c r="G54">
         <v>77.59999999999999</v>
@@ -5721,28 +5721,28 @@
         <v>71.3</v>
       </c>
       <c r="M54">
-        <v>31.375136</v>
+        <v>31.978504</v>
       </c>
       <c r="N54">
-        <v>39.92486399999999</v>
+        <v>39.321496</v>
       </c>
       <c r="O54">
-        <v>11.17896192</v>
+        <v>11.01001888</v>
       </c>
       <c r="P54">
-        <v>28.74590207999999</v>
+        <v>28.31147712</v>
       </c>
       <c r="Q54">
-        <v>35.24590207999999</v>
+        <v>34.81147711999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1192512695675521</v>
+        <v>0.1205682299351272</v>
       </c>
       <c r="T54">
-        <v>1.696334170151319</v>
+        <v>1.726748959240813</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.272500109640958</v>
+        <v>2.229622749081695</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08559234806950977</v>
+        <v>0.08556456674659452</v>
       </c>
       <c r="C55">
-        <v>329.9939298533488</v>
+        <v>322.44940238482</v>
       </c>
       <c r="D55">
-        <v>674.2739298533488</v>
+        <v>674.68940238482</v>
       </c>
       <c r="E55">
-        <v>253.48</v>
+        <v>261.4400000000001</v>
       </c>
       <c r="F55">
-        <v>421.88</v>
+        <v>429.84</v>
       </c>
       <c r="G55">
         <v>77.59999999999999</v>
@@ -5803,28 +5803,28 @@
         <v>71.3</v>
       </c>
       <c r="M55">
-        <v>31.978504</v>
+        <v>32.581872</v>
       </c>
       <c r="N55">
-        <v>39.321496</v>
+        <v>38.71812799999999</v>
       </c>
       <c r="O55">
-        <v>11.01001888</v>
+        <v>10.84107584</v>
       </c>
       <c r="P55">
-        <v>28.31147712</v>
+        <v>27.87705215999999</v>
       </c>
       <c r="Q55">
-        <v>34.81147711999999</v>
+        <v>34.37705215999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1205682299351272</v>
+        <v>0.1219424494491185</v>
       </c>
       <c r="T55">
-        <v>1.726748959240813</v>
+        <v>1.758486130464631</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.229622749081695</v>
+        <v>2.188333438913515</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08556456674659452</v>
+        <v>0.08553678542367928</v>
       </c>
       <c r="C56">
-        <v>322.44940238482</v>
+        <v>314.9053872417579</v>
       </c>
       <c r="D56">
-        <v>674.68940238482</v>
+        <v>675.1053872417579</v>
       </c>
       <c r="E56">
-        <v>261.4400000000001</v>
+        <v>269.4</v>
       </c>
       <c r="F56">
-        <v>429.84</v>
+        <v>437.8</v>
       </c>
       <c r="G56">
         <v>77.59999999999999</v>
@@ -5885,28 +5885,28 @@
         <v>71.3</v>
       </c>
       <c r="M56">
-        <v>32.581872</v>
+        <v>33.18524</v>
       </c>
       <c r="N56">
-        <v>38.71812799999999</v>
+        <v>38.11476</v>
       </c>
       <c r="O56">
-        <v>10.84107584</v>
+        <v>10.6721328</v>
       </c>
       <c r="P56">
-        <v>27.87705215999999</v>
+        <v>27.4426272</v>
       </c>
       <c r="Q56">
-        <v>34.37705215999999</v>
+        <v>33.9426272</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1219424494491185</v>
+        <v>0.1233777453859539</v>
       </c>
       <c r="T56">
-        <v>1.758486130464631</v>
+        <v>1.791633842631731</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.188333438913515</v>
+        <v>2.148545558205997</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08553678542367928</v>
+        <v>0.08550900410076401</v>
       </c>
       <c r="C57">
-        <v>314.9053872417579</v>
+        <v>307.361885372382</v>
       </c>
       <c r="D57">
-        <v>675.1053872417579</v>
+        <v>675.521885372382</v>
       </c>
       <c r="E57">
-        <v>269.4</v>
+        <v>277.36</v>
       </c>
       <c r="F57">
-        <v>437.8</v>
+        <v>445.76</v>
       </c>
       <c r="G57">
         <v>77.59999999999999</v>
@@ -5967,28 +5967,28 @@
         <v>71.3</v>
       </c>
       <c r="M57">
-        <v>33.18524</v>
+        <v>33.788608</v>
       </c>
       <c r="N57">
-        <v>38.11476</v>
+        <v>37.51139199999999</v>
       </c>
       <c r="O57">
-        <v>10.6721328</v>
+        <v>10.50318976</v>
       </c>
       <c r="P57">
-        <v>27.4426272</v>
+        <v>27.00820224</v>
       </c>
       <c r="Q57">
-        <v>33.9426272</v>
+        <v>33.50820224</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1233777453859539</v>
+        <v>0.124878282047191</v>
       </c>
       <c r="T57">
-        <v>1.791633842631731</v>
+        <v>1.826288268988244</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.148545558205997</v>
+        <v>2.110178673238033</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08550900410076401</v>
+        <v>0.08548122277784875</v>
       </c>
       <c r="C58">
-        <v>307.361885372382</v>
+        <v>299.8188977272526</v>
       </c>
       <c r="D58">
-        <v>675.521885372382</v>
+        <v>675.9388977272527</v>
       </c>
       <c r="E58">
-        <v>277.36</v>
+        <v>285.3200000000001</v>
       </c>
       <c r="F58">
-        <v>445.76</v>
+        <v>453.72</v>
       </c>
       <c r="G58">
         <v>77.59999999999999</v>
@@ -6049,28 +6049,28 @@
         <v>71.3</v>
       </c>
       <c r="M58">
-        <v>33.788608</v>
+        <v>34.39197600000001</v>
       </c>
       <c r="N58">
-        <v>37.51139199999999</v>
+        <v>36.90802399999999</v>
       </c>
       <c r="O58">
-        <v>10.50318976</v>
+        <v>10.33424672</v>
       </c>
       <c r="P58">
-        <v>27.00820224</v>
+        <v>26.57377727999999</v>
       </c>
       <c r="Q58">
-        <v>33.50820224</v>
+        <v>33.07377727999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.124878282047191</v>
+        <v>0.1264486111112762</v>
       </c>
       <c r="T58">
-        <v>1.826288268988244</v>
+        <v>1.862554529128781</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.110178673238033</v>
+        <v>2.073157994760173</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08548122277784875</v>
+        <v>0.08545344145493351</v>
       </c>
       <c r="C59">
-        <v>299.8188977272526</v>
+        <v>292.2764252592785</v>
       </c>
       <c r="D59">
-        <v>675.9388977272527</v>
+        <v>676.3564252592786</v>
       </c>
       <c r="E59">
-        <v>285.3200000000001</v>
+        <v>293.2800000000001</v>
       </c>
       <c r="F59">
-        <v>453.72</v>
+        <v>461.6800000000001</v>
       </c>
       <c r="G59">
         <v>77.59999999999999</v>
@@ -6131,28 +6131,28 @@
         <v>71.3</v>
       </c>
       <c r="M59">
-        <v>34.39197600000001</v>
+        <v>34.99534400000001</v>
       </c>
       <c r="N59">
-        <v>36.90802399999999</v>
+        <v>36.30465599999999</v>
       </c>
       <c r="O59">
-        <v>10.33424672</v>
+        <v>10.16530368</v>
       </c>
       <c r="P59">
-        <v>26.57377727999999</v>
+        <v>26.13935231999999</v>
       </c>
       <c r="Q59">
-        <v>33.07377727999999</v>
+        <v>32.63935231999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1264486111112762</v>
+        <v>0.1280937177498417</v>
       </c>
       <c r="T59">
-        <v>1.862554529128781</v>
+        <v>1.900547754037915</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.073157994760173</v>
+        <v>2.037413891402238</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08545344145493353</v>
+        <v>0.08542566013201827</v>
       </c>
       <c r="C60">
-        <v>292.2764252592784</v>
+        <v>284.7344689237252</v>
       </c>
       <c r="D60">
-        <v>676.3564252592784</v>
+        <v>676.7744689237252</v>
       </c>
       <c r="E60">
-        <v>293.28</v>
+        <v>301.24</v>
       </c>
       <c r="F60">
-        <v>461.6799999999999</v>
+        <v>469.64</v>
       </c>
       <c r="G60">
         <v>77.59999999999999</v>
@@ -6213,28 +6213,28 @@
         <v>71.3</v>
       </c>
       <c r="M60">
-        <v>34.995344</v>
+        <v>35.598712</v>
       </c>
       <c r="N60">
-        <v>36.304656</v>
+        <v>35.701288</v>
       </c>
       <c r="O60">
-        <v>10.16530368</v>
+        <v>9.996360640000001</v>
       </c>
       <c r="P60">
-        <v>26.13935232</v>
+        <v>25.70492736</v>
       </c>
       <c r="Q60">
-        <v>32.63935232</v>
+        <v>32.20492736</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1280937177498417</v>
+        <v>0.1298190734927275</v>
       </c>
       <c r="T60">
-        <v>1.900547754037915</v>
+        <v>1.940394306991397</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.037413891402239</v>
+        <v>2.002881452564913</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08542566013201827</v>
+        <v>0.09153227880910302</v>
       </c>
       <c r="C61">
-        <v>284.7344689237252</v>
+        <v>195.8252259898383</v>
       </c>
       <c r="D61">
-        <v>676.7744689237252</v>
+        <v>595.8252259898383</v>
       </c>
       <c r="E61">
-        <v>301.24</v>
+        <v>309.1999999999999</v>
       </c>
       <c r="F61">
-        <v>469.64</v>
+        <v>477.6</v>
       </c>
       <c r="G61">
         <v>77.59999999999999</v>
@@ -6295,45 +6295,45 @@
         <v>71.3</v>
       </c>
       <c r="M61">
-        <v>35.598712</v>
+        <v>42.98399999999999</v>
       </c>
       <c r="N61">
-        <v>35.701288</v>
+        <v>28.316</v>
       </c>
       <c r="O61">
-        <v>9.996360640000001</v>
+        <v>7.928480000000001</v>
       </c>
       <c r="P61">
-        <v>25.70492736</v>
+        <v>20.38752</v>
       </c>
       <c r="Q61">
-        <v>32.20492736</v>
+        <v>26.88752</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1298190734927275</v>
+        <v>0.1316306970227575</v>
       </c>
       <c r="T61">
-        <v>1.940394306991397</v>
+        <v>1.982233187592553</v>
       </c>
       <c r="U61">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
         <v>0.28</v>
       </c>
       <c r="W61">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.002881452564913</v>
+        <v>1.658756746696445</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09153227880910302</v>
+        <v>0.09160673748618776</v>
       </c>
       <c r="C62">
-        <v>195.8252259898383</v>
+        <v>186.9975265805185</v>
       </c>
       <c r="D62">
-        <v>595.8252259898383</v>
+        <v>594.9575265805184</v>
       </c>
       <c r="E62">
-        <v>309.1999999999999</v>
+        <v>317.16</v>
       </c>
       <c r="F62">
-        <v>477.6</v>
+        <v>485.56</v>
       </c>
       <c r="G62">
         <v>77.59999999999999</v>
@@ -6377,28 +6377,28 @@
         <v>71.3</v>
       </c>
       <c r="M62">
-        <v>42.98399999999999</v>
+        <v>43.7004</v>
       </c>
       <c r="N62">
-        <v>28.316</v>
+        <v>27.5996</v>
       </c>
       <c r="O62">
-        <v>7.928480000000001</v>
+        <v>7.727887999999999</v>
       </c>
       <c r="P62">
-        <v>20.38752</v>
+        <v>19.871712</v>
       </c>
       <c r="Q62">
-        <v>26.88752</v>
+        <v>26.371712</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1316306970227575</v>
+        <v>0.1335352243235584</v>
       </c>
       <c r="T62">
-        <v>1.982233187592553</v>
+        <v>2.026217651814281</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.658756746696445</v>
+        <v>1.631564013144044</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09160673748618776</v>
+        <v>0.09168119616327251</v>
       </c>
       <c r="C63">
-        <v>186.9975265805185</v>
+        <v>178.1723507548809</v>
       </c>
       <c r="D63">
-        <v>594.9575265805184</v>
+        <v>594.0923507548808</v>
       </c>
       <c r="E63">
-        <v>317.16</v>
+        <v>325.12</v>
       </c>
       <c r="F63">
-        <v>485.56</v>
+        <v>493.52</v>
       </c>
       <c r="G63">
         <v>77.59999999999999</v>
@@ -6459,28 +6459,28 @@
         <v>71.3</v>
       </c>
       <c r="M63">
-        <v>43.7004</v>
+        <v>44.41679999999999</v>
       </c>
       <c r="N63">
-        <v>27.5996</v>
+        <v>26.8832</v>
       </c>
       <c r="O63">
-        <v>7.727887999999999</v>
+        <v>7.527296000000002</v>
       </c>
       <c r="P63">
-        <v>19.871712</v>
+        <v>19.355904</v>
       </c>
       <c r="Q63">
-        <v>26.371712</v>
+        <v>25.855904</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1335352243235584</v>
+        <v>0.1355399899033487</v>
       </c>
       <c r="T63">
-        <v>2.026217651814281</v>
+        <v>2.072517087837153</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.631564013144044</v>
+        <v>1.605248464544947</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09168119616327251</v>
+        <v>0.09175565484035726</v>
       </c>
       <c r="C64">
-        <v>178.1723507548809</v>
+        <v>169.3496875196707</v>
       </c>
       <c r="D64">
-        <v>594.0923507548808</v>
+        <v>593.2296875196707</v>
       </c>
       <c r="E64">
-        <v>325.12</v>
+        <v>333.08</v>
       </c>
       <c r="F64">
-        <v>493.52</v>
+        <v>501.48</v>
       </c>
       <c r="G64">
         <v>77.59999999999999</v>
@@ -6541,28 +6541,28 @@
         <v>71.3</v>
       </c>
       <c r="M64">
-        <v>44.41679999999999</v>
+        <v>45.1332</v>
       </c>
       <c r="N64">
-        <v>26.8832</v>
+        <v>26.16679999999999</v>
       </c>
       <c r="O64">
-        <v>7.527296000000002</v>
+        <v>7.326703999999999</v>
       </c>
       <c r="P64">
-        <v>19.355904</v>
+        <v>18.840096</v>
       </c>
       <c r="Q64">
-        <v>25.855904</v>
+        <v>25.340096</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1355399899033487</v>
+        <v>0.1376531211901548</v>
       </c>
       <c r="T64">
-        <v>2.072517087837153</v>
+        <v>2.121319196077478</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.605248464544947</v>
+        <v>1.579768330187091</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09175565484035726</v>
+        <v>0.09183011351744202</v>
       </c>
       <c r="C65">
-        <v>169.3496875196707</v>
+        <v>160.5295259453924</v>
       </c>
       <c r="D65">
-        <v>593.2296875196707</v>
+        <v>592.3695259453924</v>
       </c>
       <c r="E65">
-        <v>333.08</v>
+        <v>341.04</v>
       </c>
       <c r="F65">
-        <v>501.48</v>
+        <v>509.44</v>
       </c>
       <c r="G65">
         <v>77.59999999999999</v>
@@ -6623,28 +6623,28 @@
         <v>71.3</v>
       </c>
       <c r="M65">
-        <v>45.1332</v>
+        <v>45.8496</v>
       </c>
       <c r="N65">
-        <v>26.16679999999999</v>
+        <v>25.4504</v>
       </c>
       <c r="O65">
-        <v>7.326703999999999</v>
+        <v>7.126112000000001</v>
       </c>
       <c r="P65">
-        <v>18.840096</v>
+        <v>18.324288</v>
       </c>
       <c r="Q65">
-        <v>25.340096</v>
+        <v>24.824288</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1376531211901548</v>
+        <v>0.1398836486595612</v>
       </c>
       <c r="T65">
-        <v>2.121319196077478</v>
+        <v>2.172832532553376</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.579768330187091</v>
+        <v>1.555084450027918</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09183011351744202</v>
+        <v>0.09190457219452676</v>
       </c>
       <c r="C66">
-        <v>160.5295259453924</v>
+        <v>151.7118551658485</v>
       </c>
       <c r="D66">
-        <v>592.3695259453924</v>
+        <v>591.5118551658485</v>
       </c>
       <c r="E66">
-        <v>341.04</v>
+        <v>349</v>
       </c>
       <c r="F66">
-        <v>509.44</v>
+        <v>517.4</v>
       </c>
       <c r="G66">
         <v>77.59999999999999</v>
@@ -6705,28 +6705,28 @@
         <v>71.3</v>
       </c>
       <c r="M66">
-        <v>45.8496</v>
+        <v>46.566</v>
       </c>
       <c r="N66">
-        <v>25.4504</v>
+        <v>24.734</v>
       </c>
       <c r="O66">
-        <v>7.126112000000001</v>
+        <v>6.925520000000001</v>
       </c>
       <c r="P66">
-        <v>18.324288</v>
+        <v>17.80848</v>
       </c>
       <c r="Q66">
-        <v>24.824288</v>
+        <v>24.30848</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1398836486595612</v>
+        <v>0.142241634841505</v>
       </c>
       <c r="T66">
-        <v>2.172832532553376</v>
+        <v>2.227289488256468</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.555084450027918</v>
+        <v>1.531160073873642</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09190457219452676</v>
+        <v>0.09197903087161151</v>
       </c>
       <c r="C67">
-        <v>151.7118551658485</v>
+        <v>142.896664377681</v>
       </c>
       <c r="D67">
-        <v>591.5118551658485</v>
+        <v>590.656664377681</v>
       </c>
       <c r="E67">
-        <v>349</v>
+        <v>356.96</v>
       </c>
       <c r="F67">
-        <v>517.4</v>
+        <v>525.36</v>
       </c>
       <c r="G67">
         <v>77.59999999999999</v>
@@ -6787,28 +6787,28 @@
         <v>71.3</v>
       </c>
       <c r="M67">
-        <v>46.566</v>
+        <v>47.2824</v>
       </c>
       <c r="N67">
-        <v>24.734</v>
+        <v>24.01759999999999</v>
       </c>
       <c r="O67">
-        <v>6.925520000000001</v>
+        <v>6.724927999999999</v>
       </c>
       <c r="P67">
-        <v>17.80848</v>
+        <v>17.292672</v>
       </c>
       <c r="Q67">
-        <v>24.30848</v>
+        <v>23.792672</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.142241634841505</v>
+        <v>0.144738326092975</v>
       </c>
       <c r="T67">
-        <v>2.227289488256468</v>
+        <v>2.284949794295036</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.531160073873642</v>
+        <v>1.50796067881495</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09197903087161151</v>
+        <v>0.1226043784893446</v>
       </c>
       <c r="C68">
-        <v>142.896664377681</v>
+        <v>-85.32228739833374</v>
       </c>
       <c r="D68">
-        <v>590.656664377681</v>
+        <v>370.3977126016663</v>
       </c>
       <c r="E68">
-        <v>356.96</v>
+        <v>364.9200000000001</v>
       </c>
       <c r="F68">
-        <v>525.36</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="G68">
         <v>77.59999999999999</v>
@@ -6869,45 +6869,45 @@
         <v>71.3</v>
       </c>
       <c r="M68">
-        <v>47.2824</v>
+        <v>78.29137600000001</v>
       </c>
       <c r="N68">
-        <v>24.01759999999999</v>
+        <v>-6.991376000000017</v>
       </c>
       <c r="O68">
-        <v>6.724927999999999</v>
+        <v>-1.957585280000005</v>
       </c>
       <c r="P68">
-        <v>17.292672</v>
+        <v>-5.033790720000011</v>
       </c>
       <c r="Q68">
-        <v>23.792672</v>
+        <v>1.466209279999989</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.144738326092975</v>
+        <v>0.1494811530284693</v>
       </c>
       <c r="T68">
-        <v>2.284949794295036</v>
+        <v>2.394483903659799</v>
       </c>
       <c r="U68">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.28</v>
+        <v>0.2549961569202717</v>
       </c>
       <c r="W68">
-        <v>0.0648</v>
+        <v>0.1093665641641041</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.50796067881495</v>
+        <v>0.9107005604295418</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1226043784893446</v>
+        <v>0.1236143784893446</v>
       </c>
       <c r="C69">
-        <v>-85.32228739833374</v>
+        <v>-97.78214396897499</v>
       </c>
       <c r="D69">
-        <v>370.3977126016663</v>
+        <v>365.8978560310251</v>
       </c>
       <c r="E69">
-        <v>364.9200000000001</v>
+        <v>372.8800000000001</v>
       </c>
       <c r="F69">
-        <v>533.3200000000001</v>
+        <v>541.2800000000001</v>
       </c>
       <c r="G69">
         <v>77.59999999999999</v>
@@ -6951,37 +6951,37 @@
         <v>71.3</v>
       </c>
       <c r="M69">
-        <v>78.29137600000001</v>
+        <v>79.45990400000002</v>
       </c>
       <c r="N69">
-        <v>-6.991376000000017</v>
+        <v>-8.159904000000026</v>
       </c>
       <c r="O69">
-        <v>-1.957585280000005</v>
+        <v>-2.284773120000008</v>
       </c>
       <c r="P69">
-        <v>-5.033790720000011</v>
+        <v>-5.875130880000018</v>
       </c>
       <c r="Q69">
-        <v>1.466209279999989</v>
+        <v>0.6248691199999818</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1494811530284693</v>
+        <v>0.1527211890606089</v>
       </c>
       <c r="T69">
-        <v>2.394483903659799</v>
+        <v>2.469311525649168</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2549961569202717</v>
+        <v>0.2512462134361501</v>
       </c>
       <c r="W69">
-        <v>0.1093665641641041</v>
+        <v>0.1099170558675732</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9107005604295418</v>
+        <v>0.8973079051291073</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1236143784893446</v>
+        <v>0.1246243784893446</v>
       </c>
       <c r="C70">
-        <v>-97.78214396897499</v>
+        <v>-110.1339779178583</v>
       </c>
       <c r="D70">
-        <v>365.8978560310251</v>
+        <v>361.5060220821418</v>
       </c>
       <c r="E70">
-        <v>372.8800000000001</v>
+        <v>380.84</v>
       </c>
       <c r="F70">
-        <v>541.2800000000001</v>
+        <v>549.24</v>
       </c>
       <c r="G70">
         <v>77.59999999999999</v>
@@ -7033,37 +7033,37 @@
         <v>71.3</v>
       </c>
       <c r="M70">
-        <v>79.45990400000002</v>
+        <v>80.628432</v>
       </c>
       <c r="N70">
-        <v>-8.159904000000026</v>
+        <v>-9.328432000000006</v>
       </c>
       <c r="O70">
-        <v>-2.284773120000008</v>
+        <v>-2.611960960000002</v>
       </c>
       <c r="P70">
-        <v>-5.875130880000018</v>
+        <v>-6.716471040000004</v>
       </c>
       <c r="Q70">
-        <v>0.6248691199999818</v>
+        <v>-0.2164710400000045</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1527211890606089</v>
+        <v>0.1561702596754673</v>
       </c>
       <c r="T70">
-        <v>2.469311525649168</v>
+        <v>2.54896673615398</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2512462134361501</v>
+        <v>0.247604963966061</v>
       </c>
       <c r="W70">
-        <v>0.1099170558675732</v>
+        <v>0.1104515912897823</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8973079051291073</v>
+        <v>0.8843034427359321</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1246243784893446</v>
+        <v>0.1256343784893446</v>
       </c>
       <c r="C71">
-        <v>-110.1339779178583</v>
+        <v>-122.3816328633477</v>
       </c>
       <c r="D71">
-        <v>361.5060220821418</v>
+        <v>357.2183671366523</v>
       </c>
       <c r="E71">
-        <v>380.84</v>
+        <v>388.8000000000001</v>
       </c>
       <c r="F71">
-        <v>549.24</v>
+        <v>557.2</v>
       </c>
       <c r="G71">
         <v>77.59999999999999</v>
@@ -7115,37 +7115,37 @@
         <v>71.3</v>
       </c>
       <c r="M71">
-        <v>80.628432</v>
+        <v>81.79696000000001</v>
       </c>
       <c r="N71">
-        <v>-9.328432000000006</v>
+        <v>-10.49696000000002</v>
       </c>
       <c r="O71">
-        <v>-2.611960960000002</v>
+        <v>-2.939148800000005</v>
       </c>
       <c r="P71">
-        <v>-6.716471040000004</v>
+        <v>-7.55781120000001</v>
       </c>
       <c r="Q71">
-        <v>-0.2164710400000045</v>
+        <v>-1.05781120000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1561702596754673</v>
+        <v>0.1598492683313162</v>
       </c>
       <c r="T71">
-        <v>2.54896673615398</v>
+        <v>2.633932294025779</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.247604963966061</v>
+        <v>0.2440677501951173</v>
       </c>
       <c r="W71">
-        <v>0.1104515912897823</v>
+        <v>0.1109708542713568</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8843034427359321</v>
+        <v>0.871670536411133</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1256343784893446</v>
+        <v>0.1266443784893446</v>
       </c>
       <c r="C72">
-        <v>-122.3816328633477</v>
+        <v>-134.5287722117337</v>
       </c>
       <c r="D72">
-        <v>357.2183671366523</v>
+        <v>353.0312277882664</v>
       </c>
       <c r="E72">
-        <v>388.8000000000001</v>
+        <v>396.7600000000001</v>
       </c>
       <c r="F72">
-        <v>557.2</v>
+        <v>565.1600000000001</v>
       </c>
       <c r="G72">
         <v>77.59999999999999</v>
@@ -7197,37 +7197,37 @@
         <v>71.3</v>
       </c>
       <c r="M72">
-        <v>81.79696000000001</v>
+        <v>82.96548800000002</v>
       </c>
       <c r="N72">
-        <v>-10.49696000000002</v>
+        <v>-11.66548800000002</v>
       </c>
       <c r="O72">
-        <v>-2.939148800000005</v>
+        <v>-3.266336640000007</v>
       </c>
       <c r="P72">
-        <v>-7.55781120000001</v>
+        <v>-8.399151360000017</v>
       </c>
       <c r="Q72">
-        <v>-1.05781120000001</v>
+        <v>-1.899151360000017</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1598492683313162</v>
+        <v>0.1637820017220513</v>
       </c>
       <c r="T72">
-        <v>2.633932294025779</v>
+        <v>2.72475754554391</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2440677501951173</v>
+        <v>0.2406301762487071</v>
       </c>
       <c r="W72">
-        <v>0.1109708542713568</v>
+        <v>0.1114754901266898</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.871670536411133</v>
+        <v>0.8593934866025253</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1266443784893446</v>
+        <v>0.1276543784893446</v>
       </c>
       <c r="C73">
-        <v>-134.5287722117336</v>
+        <v>-146.5788895966563</v>
       </c>
       <c r="D73">
-        <v>353.0312277882664</v>
+        <v>348.9411104033437</v>
       </c>
       <c r="E73">
-        <v>396.76</v>
+        <v>404.72</v>
       </c>
       <c r="F73">
-        <v>565.16</v>
+        <v>573.12</v>
       </c>
       <c r="G73">
         <v>77.59999999999999</v>
@@ -7279,37 +7279,37 @@
         <v>71.3</v>
       </c>
       <c r="M73">
-        <v>82.96548800000001</v>
+        <v>84.134016</v>
       </c>
       <c r="N73">
-        <v>-11.66548800000001</v>
+        <v>-12.83401600000001</v>
       </c>
       <c r="O73">
-        <v>-3.266336640000003</v>
+        <v>-3.593524480000002</v>
       </c>
       <c r="P73">
-        <v>-8.399151360000008</v>
+        <v>-9.240491520000003</v>
       </c>
       <c r="Q73">
-        <v>-1.899151360000008</v>
+        <v>-2.740491520000003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1637820017220513</v>
+        <v>0.1679956446406959</v>
       </c>
       <c r="T73">
-        <v>2.724757545543909</v>
+        <v>2.82207031502762</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2406301762487071</v>
+        <v>0.2372880904674751</v>
       </c>
       <c r="W73">
-        <v>0.1114754901266898</v>
+        <v>0.1119661083193747</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8593934866025255</v>
+        <v>0.8474574659552683</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1276543784893446</v>
+        <v>0.1286643784893446</v>
       </c>
       <c r="C74">
-        <v>-146.5788895966563</v>
+        <v>-158.5353186011528</v>
       </c>
       <c r="D74">
-        <v>348.9411104033437</v>
+        <v>344.9446813988473</v>
       </c>
       <c r="E74">
-        <v>404.72</v>
+        <v>412.6800000000001</v>
       </c>
       <c r="F74">
-        <v>573.12</v>
+        <v>581.08</v>
       </c>
       <c r="G74">
         <v>77.59999999999999</v>
@@ -7361,37 +7361,37 @@
         <v>71.3</v>
       </c>
       <c r="M74">
-        <v>84.134016</v>
+        <v>85.30254400000001</v>
       </c>
       <c r="N74">
-        <v>-12.83401600000001</v>
+        <v>-14.00254400000001</v>
       </c>
       <c r="O74">
-        <v>-3.593524480000002</v>
+        <v>-3.920712320000004</v>
       </c>
       <c r="P74">
-        <v>-9.240491520000003</v>
+        <v>-10.08183168000001</v>
       </c>
       <c r="Q74">
-        <v>-2.740491520000003</v>
+        <v>-3.581831680000011</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1679956446406959</v>
+        <v>0.172521409257018</v>
       </c>
       <c r="T74">
-        <v>2.82207031502762</v>
+        <v>2.926591437806421</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2372880904674751</v>
+        <v>0.2340375686802494</v>
       </c>
       <c r="W74">
-        <v>0.1119661083193747</v>
+        <v>0.1124432849177394</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8474574659552683</v>
+        <v>0.8358484595723192</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1286643784893446</v>
+        <v>0.1296743784893446</v>
       </c>
       <c r="C75">
-        <v>-158.5353186011528</v>
+        <v>-170.4012418191875</v>
       </c>
       <c r="D75">
-        <v>344.9446813988473</v>
+        <v>341.0387581808125</v>
       </c>
       <c r="E75">
-        <v>412.6800000000001</v>
+        <v>420.64</v>
       </c>
       <c r="F75">
-        <v>581.08</v>
+        <v>589.04</v>
       </c>
       <c r="G75">
         <v>77.59999999999999</v>
@@ -7443,37 +7443,37 @@
         <v>71.3</v>
       </c>
       <c r="M75">
-        <v>85.30254400000001</v>
+        <v>86.47107200000001</v>
       </c>
       <c r="N75">
-        <v>-14.00254400000001</v>
+        <v>-15.17107200000001</v>
       </c>
       <c r="O75">
-        <v>-3.920712320000004</v>
+        <v>-4.247900160000003</v>
       </c>
       <c r="P75">
-        <v>-10.08183168000001</v>
+        <v>-10.92317184000001</v>
       </c>
       <c r="Q75">
-        <v>-3.581831680000011</v>
+        <v>-4.423171840000006</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.172521409257018</v>
+        <v>0.1773953096130572</v>
       </c>
       <c r="T75">
-        <v>2.926591437806421</v>
+        <v>3.039152646952821</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2340375686802494</v>
+        <v>0.230874898833219</v>
       </c>
       <c r="W75">
-        <v>0.1124432849177394</v>
+        <v>0.1129075648512835</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8358484595723192</v>
+        <v>0.8245532101186394</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1296743784893446</v>
+        <v>0.1306843784893446</v>
       </c>
       <c r="C76">
-        <v>-170.4012418191875</v>
+        <v>-182.1796993084358</v>
       </c>
       <c r="D76">
-        <v>341.0387581808125</v>
+        <v>337.2203006915641</v>
       </c>
       <c r="E76">
-        <v>420.64</v>
+        <v>428.6</v>
       </c>
       <c r="F76">
-        <v>589.04</v>
+        <v>597</v>
       </c>
       <c r="G76">
         <v>77.59999999999999</v>
@@ -7525,37 +7525,37 @@
         <v>71.3</v>
       </c>
       <c r="M76">
-        <v>86.47107200000001</v>
+        <v>87.6396</v>
       </c>
       <c r="N76">
-        <v>-15.17107200000001</v>
+        <v>-16.3396</v>
       </c>
       <c r="O76">
-        <v>-4.247900160000003</v>
+        <v>-4.575088000000002</v>
       </c>
       <c r="P76">
-        <v>-10.92317184000001</v>
+        <v>-11.764512</v>
       </c>
       <c r="Q76">
-        <v>-4.423171840000006</v>
+        <v>-5.264512000000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1773953096130572</v>
+        <v>0.1826591219975794</v>
       </c>
       <c r="T76">
-        <v>3.039152646952821</v>
+        <v>3.160718752830934</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.230874898833219</v>
+        <v>0.2277965668487761</v>
       </c>
       <c r="W76">
-        <v>0.1129075648512835</v>
+        <v>0.1133594639865997</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8245532101186394</v>
+        <v>0.8135591673170576</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1306843784893446</v>
+        <v>0.1316943784893446</v>
       </c>
       <c r="C77">
-        <v>-182.1796993084358</v>
+        <v>-193.8735964815032</v>
       </c>
       <c r="D77">
-        <v>337.2203006915641</v>
+        <v>333.4864035184968</v>
       </c>
       <c r="E77">
-        <v>428.6</v>
+        <v>436.5600000000001</v>
       </c>
       <c r="F77">
-        <v>597</v>
+        <v>604.96</v>
       </c>
       <c r="G77">
         <v>77.59999999999999</v>
@@ -7607,37 +7607,37 @@
         <v>71.3</v>
       </c>
       <c r="M77">
-        <v>87.6396</v>
+        <v>88.80812800000001</v>
       </c>
       <c r="N77">
-        <v>-16.3396</v>
+        <v>-17.50812800000001</v>
       </c>
       <c r="O77">
-        <v>-4.575088000000002</v>
+        <v>-4.902275840000004</v>
       </c>
       <c r="P77">
-        <v>-11.764512</v>
+        <v>-12.60585216000001</v>
       </c>
       <c r="Q77">
-        <v>-5.264512000000003</v>
+        <v>-6.105852160000008</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1826591219975794</v>
+        <v>0.1883615854141453</v>
       </c>
       <c r="T77">
-        <v>3.160718752830934</v>
+        <v>3.292415367532223</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2277965668487761</v>
+        <v>0.2247992436007659</v>
       </c>
       <c r="W77">
-        <v>0.1133594639865997</v>
+        <v>0.1137994710394076</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8135591673170576</v>
+        <v>0.8028544414313067</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1316943784893446</v>
+        <v>0.1761802888228588</v>
       </c>
       <c r="C78">
-        <v>-193.8735964815032</v>
+        <v>-311.1570908899732</v>
       </c>
       <c r="D78">
-        <v>333.4864035184968</v>
+        <v>224.1629091100268</v>
       </c>
       <c r="E78">
-        <v>436.5600000000001</v>
+        <v>444.52</v>
       </c>
       <c r="F78">
-        <v>604.96</v>
+        <v>612.92</v>
       </c>
       <c r="G78">
         <v>77.59999999999999</v>
@@ -7689,45 +7689,45 @@
         <v>71.3</v>
       </c>
       <c r="M78">
-        <v>88.80812800000001</v>
+        <v>123.074336</v>
       </c>
       <c r="N78">
-        <v>-17.50812800000001</v>
+        <v>-51.77433600000001</v>
       </c>
       <c r="O78">
-        <v>-4.902275840000004</v>
+        <v>-14.49681408</v>
       </c>
       <c r="P78">
-        <v>-12.60585216000001</v>
+        <v>-37.27752192</v>
       </c>
       <c r="Q78">
-        <v>-6.105852160000008</v>
+        <v>-30.77752192</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1883615854141453</v>
+        <v>0.2028030036213438</v>
       </c>
       <c r="T78">
-        <v>3.292415367532223</v>
+        <v>3.625935418506785</v>
       </c>
       <c r="U78">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.2247992436007659</v>
+        <v>0.1622109096733214</v>
       </c>
       <c r="W78">
-        <v>0.1137994710394076</v>
+        <v>0.1682280493375971</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.8028544414313067</v>
+        <v>0.5793246774047189</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1761802888228588</v>
+        <v>0.1777302888228589</v>
       </c>
       <c r="C79">
-        <v>-311.1570908899732</v>
+        <v>-321.6485791611348</v>
       </c>
       <c r="D79">
-        <v>224.1629091100268</v>
+        <v>221.6314208388652</v>
       </c>
       <c r="E79">
-        <v>444.52</v>
+        <v>452.48</v>
       </c>
       <c r="F79">
-        <v>612.92</v>
+        <v>620.88</v>
       </c>
       <c r="G79">
         <v>77.59999999999999</v>
@@ -7771,37 +7771,37 @@
         <v>71.3</v>
       </c>
       <c r="M79">
-        <v>123.074336</v>
+        <v>124.672704</v>
       </c>
       <c r="N79">
-        <v>-51.77433600000001</v>
+        <v>-53.372704</v>
       </c>
       <c r="O79">
-        <v>-14.49681408</v>
+        <v>-14.94435712</v>
       </c>
       <c r="P79">
-        <v>-37.27752192</v>
+        <v>-38.42834688</v>
       </c>
       <c r="Q79">
-        <v>-30.77752192</v>
+        <v>-31.92834688</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2028030036213438</v>
+        <v>0.2099395037859503</v>
       </c>
       <c r="T79">
-        <v>3.625935418506785</v>
+        <v>3.790750664802548</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1622109096733214</v>
+        <v>0.1601312826262275</v>
       </c>
       <c r="W79">
-        <v>0.1682280493375971</v>
+        <v>0.1686456384486535</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5793246774047189</v>
+        <v>0.5718974379508124</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1777302888228589</v>
+        <v>0.1792802888228588</v>
       </c>
       <c r="C80">
-        <v>-321.6485791611348</v>
+        <v>-332.0835293533578</v>
       </c>
       <c r="D80">
-        <v>221.6314208388652</v>
+        <v>219.1564706466422</v>
       </c>
       <c r="E80">
-        <v>452.48</v>
+        <v>460.4400000000001</v>
       </c>
       <c r="F80">
-        <v>620.88</v>
+        <v>628.84</v>
       </c>
       <c r="G80">
         <v>77.59999999999999</v>
@@ -7853,37 +7853,37 @@
         <v>71.3</v>
       </c>
       <c r="M80">
-        <v>124.672704</v>
+        <v>126.271072</v>
       </c>
       <c r="N80">
-        <v>-53.372704</v>
+        <v>-54.97107200000001</v>
       </c>
       <c r="O80">
-        <v>-14.94435712</v>
+        <v>-15.39190016</v>
       </c>
       <c r="P80">
-        <v>-38.42834688</v>
+        <v>-39.57917184</v>
       </c>
       <c r="Q80">
-        <v>-31.92834688</v>
+        <v>-33.07917184</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2099395037859503</v>
+        <v>0.2177556706329003</v>
       </c>
       <c r="T80">
-        <v>3.790750664802548</v>
+        <v>3.971262601221717</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1601312826262275</v>
+        <v>0.158104304365136</v>
       </c>
       <c r="W80">
-        <v>0.1686456384486535</v>
+        <v>0.1690526556834807</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5718974379508124</v>
+        <v>0.5646582298754856</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1792802888228588</v>
+        <v>0.1808302888228588</v>
       </c>
       <c r="C81">
-        <v>-332.0835293533578</v>
+        <v>-342.463814625295</v>
       </c>
       <c r="D81">
-        <v>219.1564706466422</v>
+        <v>216.7361853747051</v>
       </c>
       <c r="E81">
-        <v>460.4400000000001</v>
+        <v>468.4000000000001</v>
       </c>
       <c r="F81">
-        <v>628.84</v>
+        <v>636.8000000000001</v>
       </c>
       <c r="G81">
         <v>77.59999999999999</v>
@@ -7935,37 +7935,37 @@
         <v>71.3</v>
       </c>
       <c r="M81">
-        <v>126.271072</v>
+        <v>127.86944</v>
       </c>
       <c r="N81">
-        <v>-54.97107200000001</v>
+        <v>-56.56944000000001</v>
       </c>
       <c r="O81">
-        <v>-15.39190016</v>
+        <v>-15.83944320000001</v>
       </c>
       <c r="P81">
-        <v>-39.57917184</v>
+        <v>-40.72999680000001</v>
       </c>
       <c r="Q81">
-        <v>-33.07917184</v>
+        <v>-34.22999680000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2177556706329003</v>
+        <v>0.2263534541645454</v>
       </c>
       <c r="T81">
-        <v>3.971262601221717</v>
+        <v>4.169825731282804</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.158104304365136</v>
+        <v>0.1561280005605718</v>
       </c>
       <c r="W81">
-        <v>0.1690526556834807</v>
+        <v>0.1694494974874372</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5646582298754856</v>
+        <v>0.557600002002042</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1808302888228588</v>
+        <v>0.1823802888228588</v>
       </c>
       <c r="C82">
-        <v>-342.463814625295</v>
+        <v>-352.7912262934709</v>
       </c>
       <c r="D82">
-        <v>216.7361853747051</v>
+        <v>214.3687737065291</v>
       </c>
       <c r="E82">
-        <v>468.4000000000001</v>
+        <v>476.36</v>
       </c>
       <c r="F82">
-        <v>636.8000000000001</v>
+        <v>644.76</v>
       </c>
       <c r="G82">
         <v>77.59999999999999</v>
@@ -8017,37 +8017,37 @@
         <v>71.3</v>
       </c>
       <c r="M82">
-        <v>127.86944</v>
+        <v>129.467808</v>
       </c>
       <c r="N82">
-        <v>-56.56944000000001</v>
+        <v>-58.16780799999999</v>
       </c>
       <c r="O82">
-        <v>-15.83944320000001</v>
+        <v>-16.28698624</v>
       </c>
       <c r="P82">
-        <v>-40.72999680000001</v>
+        <v>-41.88082175999999</v>
       </c>
       <c r="Q82">
-        <v>-34.22999680000001</v>
+        <v>-35.38082175999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2263534541645454</v>
+        <v>0.2358562675416267</v>
       </c>
       <c r="T82">
-        <v>4.169825731282804</v>
+        <v>4.389290243455583</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1561280005605718</v>
+        <v>0.1542004943808117</v>
       </c>
       <c r="W82">
-        <v>0.1694494974874372</v>
+        <v>0.169836540728333</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.557600002002042</v>
+        <v>0.5507160513600415</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1823802888228588</v>
+        <v>0.1839302888228588</v>
       </c>
       <c r="C83">
-        <v>-352.7912262934709</v>
+        <v>-363.0674782537985</v>
       </c>
       <c r="D83">
-        <v>214.3687737065291</v>
+        <v>212.0525217462015</v>
       </c>
       <c r="E83">
-        <v>476.36</v>
+        <v>484.3200000000001</v>
       </c>
       <c r="F83">
-        <v>644.76</v>
+        <v>652.72</v>
       </c>
       <c r="G83">
         <v>77.59999999999999</v>
@@ -8099,37 +8099,37 @@
         <v>71.3</v>
       </c>
       <c r="M83">
-        <v>129.467808</v>
+        <v>131.066176</v>
       </c>
       <c r="N83">
-        <v>-58.16780799999999</v>
+        <v>-59.76617600000002</v>
       </c>
       <c r="O83">
-        <v>-16.28698624</v>
+        <v>-16.73452928000001</v>
       </c>
       <c r="P83">
-        <v>-41.88082175999999</v>
+        <v>-43.03164672000001</v>
       </c>
       <c r="Q83">
-        <v>-35.38082175999999</v>
+        <v>-36.53164672000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2358562675416267</v>
+        <v>0.2464149490717171</v>
       </c>
       <c r="T83">
-        <v>4.389290243455583</v>
+        <v>4.633139701425337</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1542004943808117</v>
+        <v>0.1523200005468993</v>
       </c>
       <c r="W83">
-        <v>0.169836540728333</v>
+        <v>0.1702141438901826</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5507160513600415</v>
+        <v>0.5440000019532116</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1839302888228588</v>
+        <v>0.1854802888228588</v>
       </c>
       <c r="C84">
-        <v>-363.0674782537985</v>
+        <v>-373.2942111195122</v>
       </c>
       <c r="D84">
-        <v>212.0525217462015</v>
+        <v>209.7857888804878</v>
       </c>
       <c r="E84">
-        <v>484.3200000000001</v>
+        <v>492.2800000000001</v>
       </c>
       <c r="F84">
-        <v>652.72</v>
+        <v>660.6800000000001</v>
       </c>
       <c r="G84">
         <v>77.59999999999999</v>
@@ -8181,37 +8181,37 @@
         <v>71.3</v>
       </c>
       <c r="M84">
-        <v>131.066176</v>
+        <v>132.664544</v>
       </c>
       <c r="N84">
-        <v>-59.76617600000002</v>
+        <v>-61.36454400000001</v>
       </c>
       <c r="O84">
-        <v>-16.73452928000001</v>
+        <v>-17.18207232</v>
       </c>
       <c r="P84">
-        <v>-43.03164672000001</v>
+        <v>-44.18247168000001</v>
       </c>
       <c r="Q84">
-        <v>-36.53164672000001</v>
+        <v>-37.68247168000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2464149490717171</v>
+        <v>0.2582158284288769</v>
       </c>
       <c r="T84">
-        <v>4.633139701425337</v>
+        <v>4.905677330920946</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1523200005468993</v>
+        <v>0.1504848198174186</v>
       </c>
       <c r="W84">
-        <v>0.1702141438901826</v>
+        <v>0.1705826481806623</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5440000019532116</v>
+        <v>0.5374457850622092</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1854802888228588</v>
+        <v>0.1870302888228589</v>
       </c>
       <c r="C85">
-        <v>-373.2942111195122</v>
+        <v>-383.4729960965137</v>
       </c>
       <c r="D85">
-        <v>209.7857888804878</v>
+        <v>207.5670039034864</v>
       </c>
       <c r="E85">
-        <v>492.2800000000001</v>
+        <v>500.2400000000001</v>
       </c>
       <c r="F85">
-        <v>660.6800000000001</v>
+        <v>668.6400000000001</v>
       </c>
       <c r="G85">
         <v>77.59999999999999</v>
@@ -8263,37 +8263,37 @@
         <v>71.3</v>
       </c>
       <c r="M85">
-        <v>132.664544</v>
+        <v>134.262912</v>
       </c>
       <c r="N85">
-        <v>-61.36454400000001</v>
+        <v>-62.96291200000003</v>
       </c>
       <c r="O85">
-        <v>-17.18207232</v>
+        <v>-17.62961536000001</v>
       </c>
       <c r="P85">
-        <v>-44.18247168000001</v>
+        <v>-45.33329664000002</v>
       </c>
       <c r="Q85">
-        <v>-37.68247168000001</v>
+        <v>-38.83329664000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2582158284288769</v>
+        <v>0.2714918177056818</v>
       </c>
       <c r="T85">
-        <v>4.905677330920946</v>
+        <v>5.212282164103506</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1504848198174186</v>
+        <v>0.1486933338672112</v>
       </c>
       <c r="W85">
-        <v>0.1705826481806623</v>
+        <v>0.170942378559464</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5374457850622092</v>
+        <v>0.5310476209543257</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1870302888228588</v>
+        <v>0.1885802888228588</v>
       </c>
       <c r="C86">
-        <v>-383.4729960965136</v>
+        <v>-393.6053386153681</v>
       </c>
       <c r="D86">
-        <v>207.5670039034864</v>
+        <v>205.3946613846319</v>
       </c>
       <c r="E86">
-        <v>500.24</v>
+        <v>508.2</v>
       </c>
       <c r="F86">
-        <v>668.64</v>
+        <v>676.6</v>
       </c>
       <c r="G86">
         <v>77.59999999999999</v>
@@ -8345,37 +8345,37 @@
         <v>71.3</v>
       </c>
       <c r="M86">
-        <v>134.262912</v>
+        <v>135.86128</v>
       </c>
       <c r="N86">
-        <v>-62.962912</v>
+        <v>-64.56128000000002</v>
       </c>
       <c r="O86">
-        <v>-17.62961536</v>
+        <v>-18.07715840000001</v>
       </c>
       <c r="P86">
-        <v>-45.33329664</v>
+        <v>-46.48412160000002</v>
       </c>
       <c r="Q86">
-        <v>-38.83329664</v>
+        <v>-39.98412160000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2714918177056816</v>
+        <v>0.2865379388860604</v>
       </c>
       <c r="T86">
-        <v>5.212282164103502</v>
+        <v>5.559767641710402</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1486933338672112</v>
+        <v>0.146944000527597</v>
       </c>
       <c r="W86">
-        <v>0.170942378559464</v>
+        <v>0.1712936446940586</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5310476209543258</v>
+        <v>0.5248000018842748</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1885802888228588</v>
+        <v>0.1901302888228588</v>
       </c>
       <c r="C87">
-        <v>-393.6053386153681</v>
+        <v>-403.6926817375931</v>
       </c>
       <c r="D87">
-        <v>205.3946613846319</v>
+        <v>203.2673182624068</v>
       </c>
       <c r="E87">
-        <v>508.2</v>
+        <v>516.16</v>
       </c>
       <c r="F87">
-        <v>676.6</v>
+        <v>684.5599999999999</v>
       </c>
       <c r="G87">
         <v>77.59999999999999</v>
@@ -8427,37 +8427,37 @@
         <v>71.3</v>
       </c>
       <c r="M87">
-        <v>135.86128</v>
+        <v>137.459648</v>
       </c>
       <c r="N87">
-        <v>-64.56128000000002</v>
+        <v>-66.15964799999999</v>
       </c>
       <c r="O87">
-        <v>-18.07715840000001</v>
+        <v>-18.52470144</v>
       </c>
       <c r="P87">
-        <v>-46.48412160000002</v>
+        <v>-47.63494655999999</v>
       </c>
       <c r="Q87">
-        <v>-39.98412160000002</v>
+        <v>-41.13494655999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2865379388860604</v>
+        <v>0.3037335059493504</v>
       </c>
       <c r="T87">
-        <v>5.559767641710402</v>
+        <v>5.956893901832574</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.146944000527597</v>
+        <v>0.1452353493586714</v>
       </c>
       <c r="W87">
-        <v>0.1712936446940586</v>
+        <v>0.1716367418487788</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5248000018842748</v>
+        <v>0.5186976762809694</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1901302888228588</v>
+        <v>0.1916802888228588</v>
       </c>
       <c r="C88">
-        <v>-403.6926817375931</v>
+        <v>-413.7364093524369</v>
       </c>
       <c r="D88">
-        <v>203.2673182624068</v>
+        <v>201.1835906475631</v>
       </c>
       <c r="E88">
-        <v>516.16</v>
+        <v>524.12</v>
       </c>
       <c r="F88">
-        <v>684.5599999999999</v>
+        <v>692.52</v>
       </c>
       <c r="G88">
         <v>77.59999999999999</v>
@@ -8509,37 +8509,37 @@
         <v>71.3</v>
       </c>
       <c r="M88">
-        <v>137.459648</v>
+        <v>139.058016</v>
       </c>
       <c r="N88">
-        <v>-66.15964799999999</v>
+        <v>-67.75801600000001</v>
       </c>
       <c r="O88">
-        <v>-18.52470144</v>
+        <v>-18.97224448</v>
       </c>
       <c r="P88">
-        <v>-47.63494655999999</v>
+        <v>-48.78577152000001</v>
       </c>
       <c r="Q88">
-        <v>-41.13494655999999</v>
+        <v>-42.28577152000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3037335059493504</v>
+        <v>0.3235745448685313</v>
       </c>
       <c r="T88">
-        <v>5.956893901832574</v>
+        <v>6.415116509665849</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1452353493586714</v>
+        <v>0.1435659775269625</v>
       </c>
       <c r="W88">
-        <v>0.1716367418487788</v>
+        <v>0.1719719517125859</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5186976762809694</v>
+        <v>0.5127356340248662</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1916802888228588</v>
+        <v>0.1932302888228588</v>
       </c>
       <c r="C89">
-        <v>-413.7364093524369</v>
+        <v>-423.7378491790271</v>
       </c>
       <c r="D89">
-        <v>201.1835906475631</v>
+        <v>199.1421508209729</v>
       </c>
       <c r="E89">
-        <v>524.12</v>
+        <v>532.08</v>
       </c>
       <c r="F89">
-        <v>692.52</v>
+        <v>700.48</v>
       </c>
       <c r="G89">
         <v>77.59999999999999</v>
@@ -8591,37 +8591,37 @@
         <v>71.3</v>
       </c>
       <c r="M89">
-        <v>139.058016</v>
+        <v>140.656384</v>
       </c>
       <c r="N89">
-        <v>-67.75801600000001</v>
+        <v>-69.35638400000001</v>
       </c>
       <c r="O89">
-        <v>-18.97224448</v>
+        <v>-19.41978752</v>
       </c>
       <c r="P89">
-        <v>-48.78577152000001</v>
+        <v>-49.93659648000001</v>
       </c>
       <c r="Q89">
-        <v>-42.28577152000001</v>
+        <v>-43.43659648000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3235745448685313</v>
+        <v>0.3467224236075755</v>
       </c>
       <c r="T89">
-        <v>6.415116509665849</v>
+        <v>6.949709552138004</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1435659775269625</v>
+        <v>0.1419345459641562</v>
       </c>
       <c r="W89">
-        <v>0.1719719517125859</v>
+        <v>0.1722995431703974</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5127356340248662</v>
+        <v>0.5069090927291291</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1932302888228588</v>
+        <v>0.1947802888228588</v>
       </c>
       <c r="C90">
-        <v>-423.7378491790271</v>
+        <v>-433.6982755875766</v>
       </c>
       <c r="D90">
-        <v>199.1421508209729</v>
+        <v>197.1417244124235</v>
       </c>
       <c r="E90">
-        <v>532.08</v>
+        <v>540.0400000000001</v>
       </c>
       <c r="F90">
-        <v>700.48</v>
+        <v>708.4400000000001</v>
       </c>
       <c r="G90">
         <v>77.59999999999999</v>
@@ -8673,37 +8673,37 @@
         <v>71.3</v>
       </c>
       <c r="M90">
-        <v>140.656384</v>
+        <v>142.254752</v>
       </c>
       <c r="N90">
-        <v>-69.35638400000001</v>
+        <v>-70.95475200000003</v>
       </c>
       <c r="O90">
-        <v>-19.41978752</v>
+        <v>-19.86733056000001</v>
       </c>
       <c r="P90">
-        <v>-49.93659648000001</v>
+        <v>-51.08742144000001</v>
       </c>
       <c r="Q90">
-        <v>-43.43659648000001</v>
+        <v>-44.58742144000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3467224236075755</v>
+        <v>0.3740790075719006</v>
       </c>
       <c r="T90">
-        <v>6.949709552138004</v>
+        <v>7.581501329605095</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1419345459641562</v>
+        <v>0.1403397757847836</v>
       </c>
       <c r="W90">
-        <v>0.1722995431703974</v>
+        <v>0.1726197730224155</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5069090927291291</v>
+        <v>0.5012134849456558</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1947802888228588</v>
+        <v>0.2285953115424891</v>
       </c>
       <c r="C91">
-        <v>-433.6982755875766</v>
+        <v>-477.0954851585834</v>
       </c>
       <c r="D91">
-        <v>197.1417244124235</v>
+        <v>161.7045148414166</v>
       </c>
       <c r="E91">
-        <v>540.0400000000001</v>
+        <v>548</v>
       </c>
       <c r="F91">
-        <v>708.4400000000001</v>
+        <v>716.4</v>
       </c>
       <c r="G91">
         <v>77.59999999999999</v>
@@ -8755,45 +8755,45 @@
         <v>71.3</v>
       </c>
       <c r="M91">
-        <v>142.254752</v>
+        <v>168.92712</v>
       </c>
       <c r="N91">
-        <v>-70.95475200000003</v>
+        <v>-97.62712000000001</v>
       </c>
       <c r="O91">
-        <v>-19.86733056000001</v>
+        <v>-27.3355936</v>
       </c>
       <c r="P91">
-        <v>-51.08742144000001</v>
+        <v>-70.29152640000001</v>
       </c>
       <c r="Q91">
-        <v>-44.58742144000001</v>
+        <v>-63.79152640000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3740790075719006</v>
+        <v>0.4145571355253934</v>
       </c>
       <c r="T91">
-        <v>7.581501329605095</v>
+        <v>8.516331074489454</v>
       </c>
       <c r="U91">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1403397757847836</v>
+        <v>0.1181811422582709</v>
       </c>
       <c r="W91">
-        <v>0.1726197730224155</v>
+        <v>0.2079328866554997</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.5012134849456558</v>
+        <v>0.4220755080652532</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2285953115424891</v>
+        <v>0.2304953115424891</v>
       </c>
       <c r="C92">
-        <v>-477.0954851585834</v>
+        <v>-486.6723831547912</v>
       </c>
       <c r="D92">
-        <v>161.7045148414166</v>
+        <v>160.0876168452088</v>
       </c>
       <c r="E92">
-        <v>548</v>
+        <v>555.96</v>
       </c>
       <c r="F92">
-        <v>716.4</v>
+        <v>724.36</v>
       </c>
       <c r="G92">
         <v>77.59999999999999</v>
@@ -8837,37 +8837,37 @@
         <v>71.3</v>
       </c>
       <c r="M92">
-        <v>168.92712</v>
+        <v>170.804088</v>
       </c>
       <c r="N92">
-        <v>-97.62712000000001</v>
+        <v>-99.50408800000001</v>
       </c>
       <c r="O92">
-        <v>-27.3355936</v>
+        <v>-27.86114464000001</v>
       </c>
       <c r="P92">
-        <v>-70.29152640000001</v>
+        <v>-71.64294336</v>
       </c>
       <c r="Q92">
-        <v>-63.79152640000001</v>
+        <v>-65.14294336</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4145571355253934</v>
+        <v>0.4555301505837704</v>
       </c>
       <c r="T92">
-        <v>8.516331074489454</v>
+        <v>9.462590082766059</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1181811422582709</v>
+        <v>0.1168824483873009</v>
       </c>
       <c r="W92">
-        <v>0.2079328866554997</v>
+        <v>0.2082391186702744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4220755080652532</v>
+        <v>0.4174373156689317</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2304953115424891</v>
+        <v>0.2323953115424891</v>
       </c>
       <c r="C93">
-        <v>-486.6723831547912</v>
+        <v>-496.2172662536907</v>
       </c>
       <c r="D93">
-        <v>160.0876168452088</v>
+        <v>158.5027337463094</v>
       </c>
       <c r="E93">
-        <v>555.96</v>
+        <v>563.9200000000001</v>
       </c>
       <c r="F93">
-        <v>724.36</v>
+        <v>732.3200000000001</v>
       </c>
       <c r="G93">
         <v>77.59999999999999</v>
@@ -8919,37 +8919,37 @@
         <v>71.3</v>
       </c>
       <c r="M93">
-        <v>170.804088</v>
+        <v>172.681056</v>
       </c>
       <c r="N93">
-        <v>-99.50408800000001</v>
+        <v>-101.381056</v>
       </c>
       <c r="O93">
-        <v>-27.86114464000001</v>
+        <v>-28.38669568000001</v>
       </c>
       <c r="P93">
-        <v>-71.64294336</v>
+        <v>-72.99436032000001</v>
       </c>
       <c r="Q93">
-        <v>-65.14294336</v>
+        <v>-66.49436032000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4555301505837704</v>
+        <v>0.5067464194067418</v>
       </c>
       <c r="T93">
-        <v>9.462590082766059</v>
+        <v>10.64541384311182</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1168824483873009</v>
+        <v>0.1156119869917868</v>
       </c>
       <c r="W93">
-        <v>0.2082391186702744</v>
+        <v>0.2085386934673367</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4174373156689317</v>
+        <v>0.4128999535420955</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2323953115424891</v>
+        <v>0.2342953115424891</v>
       </c>
       <c r="C94">
-        <v>-496.2172662536907</v>
+        <v>-505.7310759859007</v>
       </c>
       <c r="D94">
-        <v>158.5027337463094</v>
+        <v>156.9489240140994</v>
       </c>
       <c r="E94">
-        <v>563.9200000000001</v>
+        <v>571.8800000000001</v>
       </c>
       <c r="F94">
-        <v>732.3200000000001</v>
+        <v>740.2800000000001</v>
       </c>
       <c r="G94">
         <v>77.59999999999999</v>
@@ -9001,37 +9001,37 @@
         <v>71.3</v>
       </c>
       <c r="M94">
-        <v>172.681056</v>
+        <v>174.558024</v>
       </c>
       <c r="N94">
-        <v>-101.381056</v>
+        <v>-103.258024</v>
       </c>
       <c r="O94">
-        <v>-28.38669568000001</v>
+        <v>-28.91224672000001</v>
       </c>
       <c r="P94">
-        <v>-72.99436032000001</v>
+        <v>-74.34577728000001</v>
       </c>
       <c r="Q94">
-        <v>-66.49436032000001</v>
+        <v>-67.84577728000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5067464194067418</v>
+        <v>0.5725959078934193</v>
       </c>
       <c r="T94">
-        <v>10.64541384311182</v>
+        <v>12.16618724927065</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1156119869917868</v>
+        <v>0.1143688473467138</v>
       </c>
       <c r="W94">
-        <v>0.2085386934673367</v>
+        <v>0.2088318257956449</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4128999535420955</v>
+        <v>0.4084601690954063</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2342953115424891</v>
+        <v>0.2361953115424891</v>
       </c>
       <c r="C95">
-        <v>-505.7310759859007</v>
+        <v>-515.214717320975</v>
       </c>
       <c r="D95">
-        <v>156.9489240140994</v>
+        <v>155.4252826790251</v>
       </c>
       <c r="E95">
-        <v>571.8800000000001</v>
+        <v>579.84</v>
       </c>
       <c r="F95">
-        <v>740.2800000000001</v>
+        <v>748.24</v>
       </c>
       <c r="G95">
         <v>77.59999999999999</v>
@@ -9083,37 +9083,37 @@
         <v>71.3</v>
       </c>
       <c r="M95">
-        <v>174.558024</v>
+        <v>176.434992</v>
       </c>
       <c r="N95">
-        <v>-103.258024</v>
+        <v>-105.134992</v>
       </c>
       <c r="O95">
-        <v>-28.91224672000001</v>
+        <v>-29.43779776000001</v>
       </c>
       <c r="P95">
-        <v>-74.34577728000001</v>
+        <v>-75.69719424000002</v>
       </c>
       <c r="Q95">
-        <v>-67.84577728000001</v>
+        <v>-69.19719424000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5725959078934193</v>
+        <v>0.6603952258756559</v>
       </c>
       <c r="T95">
-        <v>12.16618724927065</v>
+        <v>14.1938851241491</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1143688473467138</v>
+        <v>0.1131521574813232</v>
       </c>
       <c r="W95">
-        <v>0.2088318257956449</v>
+        <v>0.209118721265904</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4084601690954063</v>
+        <v>0.4041148481475828</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2361953115424891</v>
+        <v>0.2380953115424891</v>
       </c>
       <c r="C96">
-        <v>-515.214717320975</v>
+        <v>-524.6690604249916</v>
       </c>
       <c r="D96">
-        <v>155.4252826790251</v>
+        <v>153.9309395750084</v>
       </c>
       <c r="E96">
-        <v>579.84</v>
+        <v>587.8000000000001</v>
       </c>
       <c r="F96">
-        <v>748.24</v>
+        <v>756.2</v>
       </c>
       <c r="G96">
         <v>77.59999999999999</v>
@@ -9165,37 +9165,37 @@
         <v>71.3</v>
       </c>
       <c r="M96">
-        <v>176.434992</v>
+        <v>178.31196</v>
       </c>
       <c r="N96">
-        <v>-105.134992</v>
+        <v>-107.01196</v>
       </c>
       <c r="O96">
-        <v>-29.43779776000001</v>
+        <v>-29.96334880000001</v>
       </c>
       <c r="P96">
-        <v>-75.69719424000002</v>
+        <v>-77.04861120000001</v>
       </c>
       <c r="Q96">
-        <v>-69.19719424000002</v>
+        <v>-70.54861120000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6603952258756559</v>
+        <v>0.7833142710507874</v>
       </c>
       <c r="T96">
-        <v>14.1938851241491</v>
+        <v>17.03266214897893</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1131521574813232</v>
+        <v>0.1119610821394145</v>
       </c>
       <c r="W96">
-        <v>0.209118721265904</v>
+        <v>0.209399576831526</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4041148481475828</v>
+        <v>0.3998610076407662</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2380953115424891</v>
+        <v>0.2399953115424891</v>
       </c>
       <c r="C97">
-        <v>-524.6690604249916</v>
+        <v>-534.0949423177178</v>
       </c>
       <c r="D97">
-        <v>153.9309395750084</v>
+        <v>152.4650576822823</v>
       </c>
       <c r="E97">
-        <v>587.8000000000001</v>
+        <v>595.7600000000001</v>
       </c>
       <c r="F97">
-        <v>756.2</v>
+        <v>764.1600000000001</v>
       </c>
       <c r="G97">
         <v>77.59999999999999</v>
@@ -9247,37 +9247,37 @@
         <v>71.3</v>
       </c>
       <c r="M97">
-        <v>178.31196</v>
+        <v>180.188928</v>
       </c>
       <c r="N97">
-        <v>-107.01196</v>
+        <v>-108.888928</v>
       </c>
       <c r="O97">
-        <v>-29.96334880000001</v>
+        <v>-30.48889984000001</v>
       </c>
       <c r="P97">
-        <v>-77.04861120000001</v>
+        <v>-78.40002816000002</v>
       </c>
       <c r="Q97">
-        <v>-70.54861120000001</v>
+        <v>-71.90002816000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7833142710507874</v>
+        <v>0.9676928388134846</v>
       </c>
       <c r="T97">
-        <v>17.03266214897893</v>
+        <v>21.29082768622366</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1119610821394145</v>
+        <v>0.110794820867129</v>
       </c>
       <c r="W97">
-        <v>0.209399576831526</v>
+        <v>0.209674581239531</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3998610076407662</v>
+        <v>0.3956957888111748</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2399953115424891</v>
+        <v>0.2418953115424891</v>
       </c>
       <c r="C98">
-        <v>-534.0949423177177</v>
+        <v>-543.4931684359805</v>
       </c>
       <c r="D98">
-        <v>152.4650576822823</v>
+        <v>151.0268315640195</v>
       </c>
       <c r="E98">
-        <v>595.76</v>
+        <v>603.72</v>
       </c>
       <c r="F98">
-        <v>764.16</v>
+        <v>772.12</v>
       </c>
       <c r="G98">
         <v>77.59999999999999</v>
@@ -9329,37 +9329,37 @@
         <v>71.3</v>
       </c>
       <c r="M98">
-        <v>180.188928</v>
+        <v>182.065896</v>
       </c>
       <c r="N98">
-        <v>-108.888928</v>
+        <v>-110.765896</v>
       </c>
       <c r="O98">
-        <v>-30.48889984000001</v>
+        <v>-31.01445088000001</v>
       </c>
       <c r="P98">
-        <v>-78.40002816000001</v>
+        <v>-79.75144512</v>
       </c>
       <c r="Q98">
-        <v>-71.90002816000001</v>
+        <v>-73.25144512</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9676928388134821</v>
+        <v>1.27499045175131</v>
       </c>
       <c r="T98">
-        <v>21.29082768622361</v>
+        <v>28.38777024829815</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.110794820867129</v>
+        <v>0.1096526062190143</v>
       </c>
       <c r="W98">
-        <v>0.209674581239531</v>
+        <v>0.2099439154535565</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3956957888111748</v>
+        <v>0.3916164507821936</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2418953115424891</v>
+        <v>0.2437953115424891</v>
       </c>
       <c r="C99">
-        <v>-543.4931684359805</v>
+        <v>-552.8645141093798</v>
       </c>
       <c r="D99">
-        <v>151.0268315640195</v>
+        <v>149.6154858906203</v>
       </c>
       <c r="E99">
-        <v>603.72</v>
+        <v>611.6800000000001</v>
       </c>
       <c r="F99">
-        <v>772.12</v>
+        <v>780.08</v>
       </c>
       <c r="G99">
         <v>77.59999999999999</v>
@@ -9411,37 +9411,37 @@
         <v>71.3</v>
       </c>
       <c r="M99">
-        <v>182.065896</v>
+        <v>183.942864</v>
       </c>
       <c r="N99">
-        <v>-110.765896</v>
+        <v>-112.642864</v>
       </c>
       <c r="O99">
-        <v>-31.01445088000001</v>
+        <v>-31.54000192000001</v>
       </c>
       <c r="P99">
-        <v>-79.75144512</v>
+        <v>-81.10286208000001</v>
       </c>
       <c r="Q99">
-        <v>-73.25144512</v>
+        <v>-74.60286208000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.27499045175131</v>
+        <v>1.889585677626965</v>
       </c>
       <c r="T99">
-        <v>28.38777024829815</v>
+        <v>42.58165537244722</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1096526062190143</v>
+        <v>0.1085337020739223</v>
       </c>
       <c r="W99">
-        <v>0.2099439154535565</v>
+        <v>0.2102077530509691</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3916164507821936</v>
+        <v>0.3876203645497223</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2437953115424891</v>
+        <v>0.2456953115424891</v>
       </c>
       <c r="C100">
-        <v>-552.8645141093798</v>
+        <v>-562.209725954024</v>
       </c>
       <c r="D100">
-        <v>149.6154858906203</v>
+        <v>148.230274045976</v>
       </c>
       <c r="E100">
-        <v>611.6800000000001</v>
+        <v>619.64</v>
       </c>
       <c r="F100">
-        <v>780.08</v>
+        <v>788.04</v>
       </c>
       <c r="G100">
         <v>77.59999999999999</v>
@@ -9493,37 +9493,37 @@
         <v>71.3</v>
       </c>
       <c r="M100">
-        <v>183.942864</v>
+        <v>185.819832</v>
       </c>
       <c r="N100">
-        <v>-112.642864</v>
+        <v>-114.519832</v>
       </c>
       <c r="O100">
-        <v>-31.54000192000001</v>
+        <v>-32.06555296</v>
       </c>
       <c r="P100">
-        <v>-81.10286208000001</v>
+        <v>-82.45427903999999</v>
       </c>
       <c r="Q100">
-        <v>-74.60286208000001</v>
+        <v>-75.95427903999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.889585677626965</v>
+        <v>3.733371355253928</v>
       </c>
       <c r="T100">
-        <v>42.58165537244722</v>
+        <v>85.16331074489443</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1085337020739223</v>
+        <v>0.1074374020529736</v>
       </c>
       <c r="W100">
-        <v>0.2102077530509691</v>
+        <v>0.2104662605959088</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3876203645497223</v>
+        <v>0.3837050073320484</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2456953115424891</v>
-      </c>
-      <c r="C101">
-        <v>-562.209725954024</v>
-      </c>
-      <c r="D101">
-        <v>148.230274045976</v>
-      </c>
-      <c r="E101">
-        <v>619.64</v>
-      </c>
-      <c r="F101">
-        <v>788.04</v>
-      </c>
-      <c r="G101">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="H101">
-        <v>627.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>77.8</v>
-      </c>
-      <c r="K101">
-        <v>6.5</v>
-      </c>
-      <c r="L101">
-        <v>71.3</v>
-      </c>
-      <c r="M101">
-        <v>185.819832</v>
-      </c>
-      <c r="N101">
-        <v>-114.519832</v>
-      </c>
-      <c r="O101">
-        <v>-32.06555296</v>
-      </c>
-      <c r="P101">
-        <v>-82.45427903999999</v>
-      </c>
-      <c r="Q101">
-        <v>-75.95427903999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.733371355253928</v>
-      </c>
-      <c r="T101">
-        <v>85.16331074489443</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1074374020529736</v>
-      </c>
-      <c r="W101">
-        <v>0.2104662605959088</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3837050073320484</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
